--- a/results/03_LDA_Classification/artifacts/03_updated_data.xlsx
+++ b/results/03_LDA_Classification/artifacts/03_updated_data.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,6 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -478,7 +477,6 @@
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr"/>
@@ -502,11 +500,6 @@
           <t>Prob_Cluster 2</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Prob_Cluster 3</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -528,13 +521,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8930388138782234</v>
+        <v>0.9994370294159177</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006936401326307699</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1062675459891459</v>
+        <v>0.0005629705840822543</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +541,6 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -566,13 +555,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9708136619633979</v>
+        <v>0.9999857834570037</v>
       </c>
       <c r="E7" t="n">
-        <v>1.533233373565643e-05</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.02917100570286661</v>
+        <v>1.421654299628306e-05</v>
       </c>
     </row>
     <row r="8">
@@ -582,19 +568,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.407363650125292</v>
+        <v>0.9999741222957295</v>
       </c>
       <c r="E8" t="n">
-        <v>2.689390207399697e-05</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.5926094559726339</v>
+        <v>2.587770427055703e-05</v>
       </c>
     </row>
     <row r="9">
@@ -610,13 +593,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9962771469406406</v>
+        <v>0.9999745210199439</v>
       </c>
       <c r="E9" t="n">
-        <v>1.765487986729585e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.003705198179492133</v>
+        <v>2.547898005608538e-05</v>
       </c>
     </row>
     <row r="10">
@@ -632,13 +612,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9660662046043695</v>
+        <v>0.9999902171225376</v>
       </c>
       <c r="E10" t="n">
-        <v>1.09541141187131e-05</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.03392284128151161</v>
+        <v>9.782877462504263e-06</v>
       </c>
     </row>
     <row r="11">
@@ -654,13 +631,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7269429303817864</v>
+        <v>0.9996390615041485</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0004694375856183886</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.2725876320325952</v>
+        <v>0.0003609384958515414</v>
       </c>
     </row>
     <row r="12">
@@ -670,19 +644,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3798723619687696</v>
+        <v>0.9999842688420607</v>
       </c>
       <c r="E12" t="n">
-        <v>1.581074693260787e-05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.6201118272842977</v>
+        <v>1.573115793929459e-05</v>
       </c>
     </row>
     <row r="13">
@@ -698,13 +669,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9386115474909401</v>
+        <v>0.9999994993492154</v>
       </c>
       <c r="E13" t="n">
-        <v>6.672493385300438e-07</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.06138778525972145</v>
+        <v>5.006507845997768e-07</v>
       </c>
     </row>
     <row r="14">
@@ -720,13 +688,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8920144952149655</v>
+        <v>0.9999959904296857</v>
       </c>
       <c r="E14" t="n">
-        <v>5.539052395714471e-06</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.1079799657326388</v>
+        <v>4.009570314327864e-06</v>
       </c>
     </row>
     <row r="15">
@@ -736,19 +701,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2166894524773074</v>
+        <v>0.9999618477409998</v>
       </c>
       <c r="E15" t="n">
-        <v>2.549000554677754e-05</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.7832850575171457</v>
+        <v>3.815225900021037e-05</v>
       </c>
     </row>
     <row r="16">
@@ -758,19 +720,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3241609347885233</v>
+        <v>0.9992937713673032</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000586221832409631</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.675252843379067</v>
+        <v>0.0007062286326967538</v>
       </c>
     </row>
     <row r="17">
@@ -786,13 +745,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8459740439589816</v>
+        <v>0.9999763167261023</v>
       </c>
       <c r="E17" t="n">
-        <v>3.257087933904886e-05</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.1539933851616793</v>
+        <v>2.368327389768836e-05</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +764,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7203480903417181</v>
+        <v>0.9999965441635336</v>
       </c>
       <c r="E18" t="n">
-        <v>4.98599877923753e-06</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.2796469236595025</v>
+        <v>3.455836466437804e-06</v>
       </c>
     </row>
     <row r="19">
@@ -824,19 +777,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01588601899355165</v>
+        <v>0.9438582884224705</v>
       </c>
       <c r="E19" t="n">
-        <v>0.004572242718694737</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9795417382877537</v>
+        <v>0.05614171157752942</v>
       </c>
     </row>
     <row r="20">
@@ -852,13 +802,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6331765229255961</v>
+        <v>0.9999924551840922</v>
       </c>
       <c r="E20" t="n">
-        <v>1.025625673756334e-05</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.3668132208176664</v>
+        <v>7.544815907780561e-06</v>
       </c>
     </row>
     <row r="21">
@@ -868,19 +815,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02531652604893406</v>
+        <v>0.6149291386146059</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06465158772036279</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9100318862307032</v>
+        <v>0.3850708613853942</v>
       </c>
     </row>
     <row r="22">
@@ -890,19 +834,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02827924112794309</v>
+        <v>0.9999718695998208</v>
       </c>
       <c r="E22" t="n">
-        <v>4.033279439138822e-06</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9717167255926177</v>
+        <v>2.813040017928032e-05</v>
       </c>
     </row>
     <row r="23">
@@ -918,13 +859,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8042273762696682</v>
+        <v>0.9999992072475127</v>
       </c>
       <c r="E23" t="n">
-        <v>1.192773803147566e-06</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.1957714309565286</v>
+        <v>7.927524873708793e-07</v>
       </c>
     </row>
     <row r="24">
@@ -934,19 +872,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09936776890551365</v>
+        <v>0.9864138737364927</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00450427961778782</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.8961279514766984</v>
+        <v>0.01358612626350729</v>
       </c>
     </row>
     <row r="25">
@@ -962,13 +897,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6099459913563543</v>
+        <v>0.9999998687132159</v>
       </c>
       <c r="E25" t="n">
-        <v>1.92600676074784e-07</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.3900538160429697</v>
+        <v>1.312867840678461e-07</v>
       </c>
     </row>
     <row r="26">
@@ -978,19 +910,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06836790084241927</v>
+        <v>0.5662348078346129</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1649677312432362</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.7666643679143446</v>
+        <v>0.4337651921653872</v>
       </c>
     </row>
     <row r="27">
@@ -1000,19 +929,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3739277814844172</v>
+        <v>0.9999999930038727</v>
       </c>
       <c r="E27" t="n">
-        <v>8.294095908044355e-09</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.6260722102214868</v>
+        <v>6.996127367399476e-09</v>
       </c>
     </row>
     <row r="28">
@@ -1028,13 +954,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.761732892803988</v>
+        <v>0.9999779006811235</v>
       </c>
       <c r="E28" t="n">
-        <v>3.083821936797478e-05</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.2382362689766439</v>
+        <v>2.209931887653501e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1044,19 +967,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1707985665141502</v>
+        <v>0.9928472672716435</v>
       </c>
       <c r="E29" t="n">
-        <v>0.003587801352945176</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.8256136321329045</v>
+        <v>0.00715273272835645</v>
       </c>
     </row>
     <row r="30">
@@ -1072,13 +992,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1.174983218021292e-07</v>
+        <v>2.463383265149943e-07</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9999988598080363</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.02269364192225e-06</v>
+        <v>0.9999997536616735</v>
       </c>
     </row>
     <row r="31">
@@ -1088,19 +1005,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.07378597804961931</v>
+        <v>0.9994021114908841</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0001676547954511578</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.9260463671549295</v>
+        <v>0.000597888509115896</v>
       </c>
     </row>
     <row r="32">
@@ -1116,13 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>7.628052134504737e-27</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>4.132148238418022e-23</v>
       </c>
     </row>
     <row r="33">
@@ -1138,13 +1049,10 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1.065836131500787e-08</v>
+        <v>3.270204973482294e-08</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9999993312558475</v>
-      </c>
-      <c r="F33" t="n">
-        <v>6.580857912729207e-07</v>
+        <v>0.9999999672979503</v>
       </c>
     </row>
     <row r="34">
@@ -1154,19 +1062,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.05562084311562709</v>
+        <v>0.9999397647106637</v>
       </c>
       <c r="E34" t="n">
-        <v>1.431923909751288e-05</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.9443648376452753</v>
+        <v>6.023528933634769e-05</v>
       </c>
     </row>
     <row r="35">
@@ -1176,19 +1081,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0141825797370265</v>
+        <v>0.9833197826682381</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00122912330692003</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.9845882969560534</v>
+        <v>0.01668021733176197</v>
       </c>
     </row>
     <row r="36">
@@ -1204,13 +1106,10 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>4.571994379392449e-12</v>
+        <v>1.330913157460145e-11</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9999999994946862</v>
-      </c>
-      <c r="F36" t="n">
-        <v>5.007418601060551e-10</v>
+        <v>0.9999999999866909</v>
       </c>
     </row>
     <row r="37">
@@ -1220,19 +1119,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.004203307588160066</v>
+        <v>0.6888056619438209</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01173392198228013</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.9840627704295599</v>
+        <v>0.3111943380561791</v>
       </c>
     </row>
     <row r="38">
@@ -1248,13 +1144,10 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9646059822041684</v>
+        <v>0.9999996426562661</v>
       </c>
       <c r="E38" t="n">
-        <v>4.348716715537421e-07</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.03539358292416005</v>
+        <v>3.573437339069683e-07</v>
       </c>
     </row>
     <row r="39">
@@ -1270,13 +1163,10 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9033825068889969</v>
+        <v>0.9996345238959438</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0004489054242668938</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.0961685876867362</v>
+        <v>0.0003654761040562116</v>
       </c>
     </row>
     <row r="40">
@@ -1286,19 +1176,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08708133303814967</v>
+        <v>0.9953528749922381</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001416597841688897</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.9115020691201614</v>
+        <v>0.004647125007761838</v>
       </c>
     </row>
     <row r="41">
@@ -1308,19 +1195,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4115494971099738</v>
+        <v>0.9999957324607841</v>
       </c>
       <c r="E41" t="n">
-        <v>4.650419195724836e-06</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.5884458524708305</v>
+        <v>4.267539215905691e-06</v>
       </c>
     </row>
     <row r="42">
@@ -1336,13 +1220,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.001102972406650756</v>
+        <v>0.003147783727003306</v>
       </c>
       <c r="E42" t="n">
-        <v>0.984944878269835</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.01395214932351421</v>
+        <v>0.9968522162729967</v>
       </c>
     </row>
     <row r="43">
@@ -1358,13 +1239,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.658058997307677e-08</v>
+        <v>2.761256345795715e-08</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9999999204147642</v>
-      </c>
-      <c r="F43" t="n">
-        <v>6.300464578438338e-08</v>
+        <v>0.9999999723874365</v>
       </c>
     </row>
     <row r="44">
@@ -1374,19 +1252,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1659659557823189</v>
+        <v>0.9999883054126635</v>
       </c>
       <c r="E44" t="n">
-        <v>6.604462492445841e-06</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.8340274397551887</v>
+        <v>1.169458733648802e-05</v>
       </c>
     </row>
     <row r="45">
@@ -1402,13 +1277,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4763693016782979</v>
+        <v>0.9456638320097462</v>
       </c>
       <c r="E45" t="n">
-        <v>0.05385228955914349</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.4697784087625586</v>
+        <v>0.05433616799025372</v>
       </c>
     </row>
     <row r="46">
@@ -1418,19 +1290,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1821838746236809</v>
+        <v>0.9902985946765539</v>
       </c>
       <c r="E46" t="n">
-        <v>0.005078189472486301</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.8127379359038328</v>
+        <v>0.009701405323446105</v>
       </c>
     </row>
     <row r="47">
@@ -1446,13 +1315,10 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6736997588700759</v>
+        <v>0.9999992613169872</v>
       </c>
       <c r="E47" t="n">
-        <v>1.083266502096647e-06</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.326299157863422</v>
+        <v>7.386830127213638e-07</v>
       </c>
     </row>
     <row r="48">
@@ -1468,13 +1334,10 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9454342789635214</v>
+        <v>0.9999999957735648</v>
       </c>
       <c r="E48" t="n">
-        <v>6.154195513919144e-09</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.05456571488228311</v>
+        <v>4.226435223288692e-09</v>
       </c>
     </row>
     <row r="49">
@@ -1490,13 +1353,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6258633958741904</v>
+        <v>0.9852124293345479</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01691532694032227</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.3572212771854875</v>
+        <v>0.01478757066545206</v>
       </c>
     </row>
     <row r="50">
@@ -1512,13 +1372,10 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2859396932701364</v>
+        <v>0.3899123167824377</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6289897452144185</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.08507056151544515</v>
+        <v>0.6100876832175623</v>
       </c>
     </row>
     <row r="51">
@@ -1534,13 +1391,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9371070579726012</v>
+        <v>0.9999993763333088</v>
       </c>
       <c r="E51" t="n">
-        <v>8.303902447713778e-07</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.06289211163715415</v>
+        <v>6.236666912014923e-07</v>
       </c>
     </row>
     <row r="52">
@@ -1556,13 +1410,10 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9259457430223216</v>
+        <v>0.9998795740465153</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0001459982336347868</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.07390825874404365</v>
+        <v>0.0001204259534847385</v>
       </c>
     </row>
     <row r="53">
@@ -1578,13 +1429,10 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6284018784724213</v>
+        <v>0.9982271040127696</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0021232383634781</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.3694748831641006</v>
+        <v>0.001772895987230412</v>
       </c>
     </row>
     <row r="54">
@@ -1594,19 +1442,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4834237531430888</v>
+        <v>0.9998612853304305</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0001539796652154653</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.5164222671916958</v>
+        <v>0.0001387146695694419</v>
       </c>
     </row>
     <row r="55">
@@ -1622,13 +1467,10 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8588821447921057</v>
+        <v>0.9960077573652154</v>
       </c>
       <c r="E55" t="n">
-        <v>0.004833623163701548</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.1362842320441928</v>
+        <v>0.003992242634784542</v>
       </c>
     </row>
     <row r="56">
@@ -1644,13 +1486,10 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7001071749721947</v>
+        <v>0.9988983167485165</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001384572968220394</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.298508252059585</v>
+        <v>0.001101683251483495</v>
       </c>
     </row>
     <row r="57">
@@ -1666,13 +1505,10 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0.02079652005312868</v>
+        <v>0.0484273128490893</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9119609285787589</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.06724255136811241</v>
+        <v>0.9515726871509107</v>
       </c>
     </row>
     <row r="58">
@@ -1688,13 +1524,10 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9594862111778263</v>
+        <v>0.9999676382796191</v>
       </c>
       <c r="E58" t="n">
-        <v>3.645279453895207e-05</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.04047733602763482</v>
+        <v>3.236172038091091e-05</v>
       </c>
     </row>
     <row r="59">
@@ -1710,13 +1543,10 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0.50495452831442</v>
+        <v>0.9840957376352911</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01638386615844437</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.4786616055271357</v>
+        <v>0.01590426236470893</v>
       </c>
     </row>
     <row r="60">
@@ -1732,13 +1562,10 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3604382108756895</v>
+        <v>0.4529492582960561</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5664098448984147</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.07315194422589567</v>
+        <v>0.5470507417039439</v>
       </c>
     </row>
     <row r="61">
@@ -1748,14 +1575,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1770,13 +1596,10 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.05059777787523043</v>
+        <v>0.08165278453545599</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9151233938873641</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.03427882823740542</v>
+        <v>0.918347215464544</v>
       </c>
     </row>
     <row r="63">
@@ -1786,19 +1609,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0.06870051263688146</v>
+        <v>0.7083137603173533</v>
       </c>
       <c r="E63" t="n">
-        <v>0.09207872226745646</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.839220765095662</v>
+        <v>0.2916862396826468</v>
       </c>
     </row>
     <row r="64">
@@ -1814,13 +1634,10 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9559401897783785</v>
+        <v>0.999978960664349</v>
       </c>
       <c r="E64" t="n">
-        <v>2.430456781312665e-05</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.04403550565380861</v>
+        <v>2.103933565105146e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1830,19 +1647,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1641344579676876</v>
+        <v>0.5816233976978904</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2862331299385792</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.5496324120937331</v>
+        <v>0.4183766023021095</v>
       </c>
     </row>
     <row r="66">
@@ -1852,19 +1666,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3938108610279972</v>
+        <v>0.999978613703595</v>
       </c>
       <c r="E66" t="n">
-        <v>2.184684435111248e-05</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.6061672921276517</v>
+        <v>2.13862964049752e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1880,13 +1691,10 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9954705924137439</v>
+        <v>0.9992515018709702</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0004894660364054345</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.004039941549850653</v>
+        <v>0.0007484981290298248</v>
       </c>
     </row>
     <row r="68">
@@ -1902,13 +1710,10 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8533151778932658</v>
+        <v>0.9998643665634882</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0001785654036165715</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.1465062567031175</v>
+        <v>0.0001356334365118155</v>
       </c>
     </row>
     <row r="69">
@@ -1918,19 +1723,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3675704229396111</v>
+        <v>0.9493563868868471</v>
       </c>
       <c r="E69" t="n">
-        <v>0.04296045069562027</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.5894691263647687</v>
+        <v>0.05064361311315295</v>
       </c>
     </row>
     <row r="70">
@@ -1946,13 +1748,10 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9081386742504323</v>
+        <v>0.9999492101956737</v>
       </c>
       <c r="E70" t="n">
-        <v>6.483370049648972e-05</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.09179649204907143</v>
+        <v>5.078980432629481e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1968,13 +1767,10 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9463847860038482</v>
+        <v>0.9999977778324606</v>
       </c>
       <c r="E71" t="n">
-        <v>2.797774203538734e-06</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.05361241622194833</v>
+        <v>2.222167539425228e-06</v>
       </c>
     </row>
     <row r="72">
@@ -1990,13 +1786,10 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9499816951195361</v>
+        <v>0.9999969033545016</v>
       </c>
       <c r="E72" t="n">
-        <v>3.822701111237312e-06</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.05001448217935283</v>
+        <v>3.096645498381546e-06</v>
       </c>
     </row>
     <row r="73">
@@ -2012,13 +1805,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5247914225553154</v>
+        <v>0.6563552684720735</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3662030630607029</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.1090055143839816</v>
+        <v>0.3436447315279265</v>
       </c>
     </row>
     <row r="74">
@@ -2034,13 +1824,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9037613552335333</v>
+        <v>0.9959833556379938</v>
       </c>
       <c r="E74" t="n">
-        <v>0.004640766238030584</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.09159787852843602</v>
+        <v>0.004016644362006175</v>
       </c>
     </row>
     <row r="75">
@@ -2056,13 +1843,10 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9268661426364219</v>
+        <v>0.9975055905634014</v>
       </c>
       <c r="E75" t="n">
-        <v>0.002801151650573916</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.07033270571300421</v>
+        <v>0.00249440943659861</v>
       </c>
     </row>
     <row r="76">
@@ -2078,13 +1862,10 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.002613710669044969</v>
+        <v>0.002779264079736388</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9970062479852934</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.0003800413456617034</v>
+        <v>0.9972207359202636</v>
       </c>
     </row>
     <row r="77">
@@ -2100,13 +1881,10 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9307649696034134</v>
+        <v>0.9999939866372628</v>
       </c>
       <c r="E77" t="n">
-        <v>7.724191011718138e-06</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.06922730620557493</v>
+        <v>6.013362737230287e-06</v>
       </c>
     </row>
     <row r="78">
@@ -2122,13 +1900,10 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9880638671573381</v>
+        <v>0.9999137354397027</v>
       </c>
       <c r="E78" t="n">
-        <v>7.443029624333385e-05</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.01186170254641847</v>
+        <v>8.6264560297234e-05</v>
       </c>
     </row>
     <row r="79">
@@ -2144,13 +1919,10 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9943704204256851</v>
+        <v>0.9994082542556327</v>
       </c>
       <c r="E79" t="n">
-        <v>0.000410921846465184</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.005218657727849511</v>
+        <v>0.0005917457443672268</v>
       </c>
     </row>
     <row r="80">
@@ -2166,13 +1938,10 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9616666203553391</v>
+        <v>0.9999999333377995</v>
       </c>
       <c r="E80" t="n">
-        <v>8.5553439262409e-08</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.03833329409122171</v>
+        <v>6.666220056203019e-08</v>
       </c>
     </row>
     <row r="81">
@@ -2188,13 +1957,10 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9173001879908256</v>
+        <v>0.9999984460096433</v>
       </c>
       <c r="E81" t="n">
-        <v>2.115460872174184e-06</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.08269769654830236</v>
+        <v>1.553990356734324e-06</v>
       </c>
     </row>
     <row r="82">
@@ -2210,13 +1976,10 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9926100230436273</v>
+        <v>0.994667596815629</v>
       </c>
       <c r="E82" t="n">
-        <v>0.003343499836863423</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.004046477119509125</v>
+        <v>0.00533240318437095</v>
       </c>
     </row>
     <row r="83">
@@ -2232,13 +1995,10 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5435391136508937</v>
+        <v>0.9999949218310719</v>
       </c>
       <c r="E83" t="n">
-        <v>6.4830356142786e-06</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.4564544033134919</v>
+        <v>5.078168928134574e-06</v>
       </c>
     </row>
     <row r="84">
@@ -2254,13 +2014,10 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9301571220072643</v>
+        <v>0.9935697432487105</v>
       </c>
       <c r="E84" t="n">
-        <v>0.006943321852644946</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.06289955614009084</v>
+        <v>0.006430256751289528</v>
       </c>
     </row>
     <row r="85">
@@ -2276,13 +2033,10 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9320406945013249</v>
+        <v>0.9999980543417524</v>
       </c>
       <c r="E85" t="n">
-        <v>2.556531444978715e-06</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.06795674896723007</v>
+        <v>1.945658247597983e-06</v>
       </c>
     </row>
     <row r="86">
@@ -2298,13 +2052,10 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.800195900092966</v>
+        <v>0.8807366740548866</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1251147568110145</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.07468934309601942</v>
+        <v>0.1192633259451134</v>
       </c>
     </row>
     <row r="87">
@@ -2320,13 +2071,10 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9823435738604881</v>
+        <v>0.9998052421714775</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0001786943926912858</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.01747773174682065</v>
+        <v>0.0001947578285224935</v>
       </c>
     </row>
     <row r="88">
@@ -2342,13 +2090,10 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9707579289185299</v>
+        <v>0.9999996954282625</v>
       </c>
       <c r="E88" t="n">
-        <v>3.58625884839712e-07</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.02924171245558537</v>
+        <v>3.045717374427348e-07</v>
       </c>
     </row>
     <row r="89">
@@ -2358,19 +2103,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4356184253907948</v>
+        <v>0.9984010567424756</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00157916148724887</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.5628024131219563</v>
+        <v>0.001598943257524389</v>
       </c>
     </row>
     <row r="90">
@@ -2386,13 +2128,10 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5426449812801051</v>
+        <v>0.9998784640792086</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0001442387057220378</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.4572107800141729</v>
+        <v>0.0001215359207914966</v>
       </c>
     </row>
     <row r="91">
@@ -2408,13 +2147,10 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.7655550091115562</v>
+        <v>0.9999999197082675</v>
       </c>
       <c r="E91" t="n">
-        <v>1.273510939935604e-07</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.2344448635373499</v>
+        <v>8.029173244055565e-08</v>
       </c>
     </row>
     <row r="92">
@@ -2430,13 +2166,10 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.6131442824963248</v>
+        <v>0.9998264672537391</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0002167211413016934</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.3866389963623734</v>
+        <v>0.0001735327462608492</v>
       </c>
     </row>
     <row r="93">
@@ -2452,13 +2185,10 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4959080683832348</v>
+        <v>0.8879388280439396</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1150723720080707</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.3890195596086944</v>
+        <v>0.1120611719560604</v>
       </c>
     </row>
     <row r="94">
@@ -2474,13 +2204,10 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.795503752095942</v>
+        <v>0.9999789974092727</v>
       </c>
       <c r="E94" t="n">
-        <v>2.936050185340181e-05</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.2044668874022045</v>
+        <v>2.100259072735807e-05</v>
       </c>
     </row>
     <row r="95">
@@ -2496,13 +2223,10 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7561862705836361</v>
+        <v>0.9999991311123034</v>
       </c>
       <c r="E95" t="n">
-        <v>1.304103335894463e-06</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.243812425313028</v>
+        <v>8.688876965758181e-07</v>
       </c>
     </row>
     <row r="96">
@@ -2512,19 +2236,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.344883475684555</v>
+        <v>0.9957045797546025</v>
       </c>
       <c r="E96" t="n">
-        <v>0.003576836714664046</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.651539687600781</v>
+        <v>0.004295420245397507</v>
       </c>
     </row>
     <row r="97">
@@ -2534,19 +2255,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2699060410990808</v>
+        <v>0.9975639072324957</v>
       </c>
       <c r="E97" t="n">
-        <v>0.001734850488893272</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.7283591084120258</v>
+        <v>0.002436092767504325</v>
       </c>
     </row>
     <row r="98">
@@ -2562,13 +2280,10 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9364669762757269</v>
+        <v>0.999970097023432</v>
       </c>
       <c r="E98" t="n">
-        <v>3.651992873741862e-05</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.06349650379553584</v>
+        <v>2.990297656806216e-05</v>
       </c>
     </row>
     <row r="99">
@@ -2584,13 +2299,10 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.7058994274605811</v>
+        <v>0.9974044074860996</v>
       </c>
       <c r="E99" t="n">
-        <v>0.003206470403571821</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.290894102135847</v>
+        <v>0.002595592513900376</v>
       </c>
     </row>
     <row r="100">
@@ -2600,19 +2312,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4250415114352595</v>
+        <v>0.888207831180719</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1059555815654312</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.4690029069993094</v>
+        <v>0.111792168819281</v>
       </c>
     </row>
     <row r="101">
@@ -2628,13 +2337,10 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0395897441409065</v>
+        <v>0.09404589050175716</v>
       </c>
       <c r="E101" t="n">
-        <v>0.8452723781111837</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.1151378777479098</v>
+        <v>0.9059541094982428</v>
       </c>
     </row>
     <row r="102">
@@ -2650,13 +2356,10 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.6826997905466288</v>
+        <v>0.9999984942229337</v>
       </c>
       <c r="E102" t="n">
-        <v>2.182081079118251e-06</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.317298027372292</v>
+        <v>1.505777066246886e-06</v>
       </c>
     </row>
     <row r="103">
@@ -2666,19 +2369,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3591612806388351</v>
+        <v>0.9917074974656341</v>
       </c>
       <c r="E103" t="n">
-        <v>0.007007569236308022</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.633831150124857</v>
+        <v>0.008292502534365843</v>
       </c>
     </row>
     <row r="104">
@@ -2695,7 +2395,6 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2704,19 +2403,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.281035204600967</v>
+        <v>0.8244063688773521</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1344874028644822</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.5844773925345509</v>
+        <v>0.1755936311226479</v>
       </c>
     </row>
     <row r="106">
@@ -2732,13 +2428,10 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.6287900928382127</v>
+        <v>0.9945521413852751</v>
       </c>
       <c r="E106" t="n">
-        <v>0.006368575607089751</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.3648413315546974</v>
+        <v>0.005447858614724835</v>
       </c>
     </row>
     <row r="107">
@@ -2754,13 +2447,10 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0.7061482635686377</v>
+        <v>0.9999111955376657</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0001184437778360108</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.2937332926535263</v>
+        <v>8.880446233428549e-05</v>
       </c>
     </row>
     <row r="108">
@@ -2776,13 +2466,10 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9553107536345441</v>
+        <v>0.9999997876638032</v>
       </c>
       <c r="E108" t="n">
-        <v>2.73026275907901e-07</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.04468897333918012</v>
+        <v>2.123361968122701e-07</v>
       </c>
     </row>
     <row r="109">
@@ -2798,13 +2485,10 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.6867271128354741</v>
+        <v>0.9999704233875857</v>
       </c>
       <c r="E109" t="n">
-        <v>4.012899887001377e-05</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.3132327581656559</v>
+        <v>2.95766124142816e-05</v>
       </c>
     </row>
     <row r="110">
@@ -2820,13 +2504,10 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9371619357975897</v>
+        <v>0.9999978193764207</v>
       </c>
       <c r="E110" t="n">
-        <v>2.821565877396431e-06</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0.06283524263653296</v>
+        <v>2.180623579252055e-06</v>
       </c>
     </row>
     <row r="111">
@@ -2842,13 +2523,10 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.946234488233011</v>
+        <v>0.9996262225163777</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0004185006864675909</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.05334701108052139</v>
+        <v>0.0003737774836223772</v>
       </c>
     </row>
     <row r="112">
@@ -2864,13 +2542,10 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9165560073187961</v>
+        <v>0.9995397724331357</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0005506818714420511</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.08289331080976188</v>
+        <v>0.00046022756686425</v>
       </c>
     </row>
     <row r="113">
@@ -2886,13 +2561,10 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.8369558010700828</v>
+        <v>0.9970459267842873</v>
       </c>
       <c r="E113" t="n">
-        <v>0.003647872162693672</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.1593963267672236</v>
+        <v>0.002954073215712733</v>
       </c>
     </row>
     <row r="114">
@@ -2908,13 +2580,10 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9861668750590032</v>
+        <v>0.9999679368733725</v>
       </c>
       <c r="E114" t="n">
-        <v>2.919839827475187e-05</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0.01380392654272186</v>
+        <v>3.206312662751521e-05</v>
       </c>
     </row>
     <row r="115">
@@ -2930,13 +2599,10 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9824861834181501</v>
+        <v>0.9999336086788486</v>
       </c>
       <c r="E115" t="n">
-        <v>6.240249543961055e-05</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0.01745141408641033</v>
+        <v>6.639132115133908e-05</v>
       </c>
     </row>
     <row r="116">
@@ -2952,13 +2618,10 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9326144528901161</v>
+        <v>0.9998591708578187</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0001675895637123496</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0.06721795754617158</v>
+        <v>0.0001408291421812583</v>
       </c>
     </row>
     <row r="117">
@@ -2974,13 +2637,10 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9588559116529521</v>
+        <v>0.9997162286102887</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0003047635758583203</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.04083932477118943</v>
+        <v>0.0002837713897112502</v>
       </c>
     </row>
     <row r="118">
@@ -2996,13 +2656,10 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9709960616906855</v>
+        <v>0.9990584684734629</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0009165138160150806</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0.02808742449329948</v>
+        <v>0.0009415315265371031</v>
       </c>
     </row>
     <row r="119">
@@ -3018,13 +2675,10 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9793422933218479</v>
+        <v>0.9999995443412794</v>
       </c>
       <c r="E119" t="n">
-        <v>4.962891097955327e-07</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.02065721038904235</v>
+        <v>4.556587206896692e-07</v>
       </c>
     </row>
     <row r="120">
@@ -3040,13 +2694,10 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.8163904717648104</v>
+        <v>0.9999812175178842</v>
       </c>
       <c r="E120" t="n">
-        <v>2.623971810207783e-05</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.1835832885170875</v>
+        <v>1.878248211584606e-05</v>
       </c>
     </row>
     <row r="121">
@@ -3062,13 +2713,10 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9412372661000433</v>
+        <v>0.9999575497692472</v>
       </c>
       <c r="E121" t="n">
-        <v>5.07643261594157e-05</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0.05871196957379733</v>
+        <v>4.245023075272756e-05</v>
       </c>
     </row>
     <row r="122">
@@ -3084,13 +2732,10 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8931594721647415</v>
+        <v>0.9999991173541274</v>
       </c>
       <c r="E122" t="n">
-        <v>1.260355159888026e-06</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.1068392674800988</v>
+        <v>8.826458726032282e-07</v>
       </c>
     </row>
     <row r="123">
@@ -3106,13 +2751,10 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0.661234739814507</v>
+        <v>0.9937536499743952</v>
       </c>
       <c r="E123" t="n">
-        <v>0.007420206929167076</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0.3313450532563258</v>
+        <v>0.006246350025604838</v>
       </c>
     </row>
     <row r="124">
@@ -3128,13 +2770,10 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9427768398937064</v>
+        <v>0.9999677106729249</v>
       </c>
       <c r="E124" t="n">
-        <v>3.868080804944561e-05</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.05718447929824417</v>
+        <v>3.228932707506022e-05</v>
       </c>
     </row>
     <row r="125">
@@ -3150,13 +2789,10 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9136035289770464</v>
+        <v>0.9999948081240377</v>
       </c>
       <c r="E125" t="n">
-        <v>6.92046921126871e-06</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.08638955055374223</v>
+        <v>5.191875962310331e-06</v>
       </c>
     </row>
     <row r="126">
@@ -3172,13 +2808,10 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.7542257769434905</v>
+        <v>0.9977518417234348</v>
       </c>
       <c r="E126" t="n">
-        <v>0.002820651265647842</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0.2429535717908617</v>
+        <v>0.002248158276565214</v>
       </c>
     </row>
     <row r="127">
@@ -3194,13 +2827,10 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.8798893896167871</v>
+        <v>0.9818037222424594</v>
       </c>
       <c r="E127" t="n">
-        <v>0.02054375142046436</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0.09956685896274846</v>
+        <v>0.01819627775754061</v>
       </c>
     </row>
     <row r="128">
@@ -3216,13 +2846,10 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3351247781272229</v>
+        <v>0.4679654807145243</v>
       </c>
       <c r="E128" t="n">
-        <v>0.5531213957546074</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0.1117538261181698</v>
+        <v>0.5320345192854757</v>
       </c>
     </row>
     <row r="129">
@@ -3238,13 +2865,10 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>2.817367537808323e-06</v>
+        <v>5.515210886430921e-06</v>
       </c>
       <c r="E129" t="n">
-        <v>0.9999842431790845</v>
-      </c>
-      <c r="F129" t="n">
-        <v>1.293945337761069e-05</v>
+        <v>0.9999944847891136</v>
       </c>
     </row>
     <row r="130">
@@ -3260,13 +2884,10 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.8036613122009528</v>
+        <v>0.9944598476726647</v>
       </c>
       <c r="E130" t="n">
-        <v>0.006801848842022435</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.1895368389570247</v>
+        <v>0.005540152327335258</v>
       </c>
     </row>
     <row r="131">
@@ -3282,13 +2903,10 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9151475755637909</v>
+        <v>0.9999994308185277</v>
       </c>
       <c r="E131" t="n">
-        <v>7.957094454356901e-07</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0.08485162872676359</v>
+        <v>5.691814722406058e-07</v>
       </c>
     </row>
     <row r="132">
@@ -3304,13 +2922,10 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5610962052160232</v>
+        <v>0.9285780847040511</v>
       </c>
       <c r="E132" t="n">
-        <v>0.07690340703868333</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.3620003877452935</v>
+        <v>0.07142191529594891</v>
       </c>
     </row>
     <row r="133">
@@ -3326,13 +2941,10 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9368390269633942</v>
+        <v>0.9999688834333027</v>
       </c>
       <c r="E133" t="n">
-        <v>3.793079963939715e-05</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0.06312304223696649</v>
+        <v>3.111656669727785e-05</v>
       </c>
     </row>
     <row r="134">
@@ -3348,13 +2960,10 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.8940542385101335</v>
+        <v>0.9999951612007786</v>
       </c>
       <c r="E134" t="n">
-        <v>6.640354243550162e-06</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.1059391211356229</v>
+        <v>4.838799221469469e-06</v>
       </c>
     </row>
     <row r="135">
@@ -3370,13 +2979,10 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9704122759257691</v>
+        <v>0.9999352164299828</v>
       </c>
       <c r="E135" t="n">
-        <v>6.765741933498584e-05</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0.02952006665489615</v>
+        <v>6.478357001711383e-05</v>
       </c>
     </row>
     <row r="136">
@@ -3392,13 +2998,10 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9944406113495206</v>
+        <v>0.9999095410985065</v>
       </c>
       <c r="E136" t="n">
-        <v>6.626329591292913e-05</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0.005493125354566306</v>
+        <v>9.045890149351691e-05</v>
       </c>
     </row>
     <row r="137">
@@ -3414,13 +3017,10 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1199283436832343</v>
+        <v>0.1336991829718509</v>
       </c>
       <c r="E137" t="n">
-        <v>0.8658408405677495</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.01423081574901616</v>
+        <v>0.8663008170281491</v>
       </c>
     </row>
     <row r="138">
@@ -3437,7 +3037,6 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -3446,19 +3045,16 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3999650178018593</v>
+        <v>0.9999915454673454</v>
       </c>
       <c r="E139" t="n">
-        <v>8.908444046299776e-06</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0.6000260737540943</v>
+        <v>8.454532654687614e-06</v>
       </c>
     </row>
     <row r="140">
@@ -3474,13 +3070,10 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.7061396881350891</v>
+        <v>0.9999948081943347</v>
       </c>
       <c r="E140" t="n">
-        <v>7.386184692168492e-06</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0.2938529256802188</v>
+        <v>5.191805665282046e-06</v>
       </c>
     </row>
     <row r="141">
@@ -3496,13 +3089,10 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.8207465882985528</v>
+        <v>0.9974487849824101</v>
       </c>
       <c r="E141" t="n">
-        <v>0.00317987146010388</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0.1760735402413432</v>
+        <v>0.002551215017589953</v>
       </c>
     </row>
     <row r="142">
@@ -3518,13 +3108,10 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9293272727608336</v>
+        <v>0.9999902175456775</v>
       </c>
       <c r="E142" t="n">
-        <v>1.246794305782308e-05</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0.07066025929610864</v>
+        <v>9.782454322526081e-06</v>
       </c>
     </row>
     <row r="143">
@@ -3534,19 +3121,16 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2742356382476484</v>
+        <v>0.999996546289818</v>
       </c>
       <c r="E143" t="n">
-        <v>2.881542672946173e-06</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0.7257614802096787</v>
+        <v>3.453710182004945e-06</v>
       </c>
     </row>
     <row r="144">
@@ -3562,13 +3146,10 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.03062557633045872</v>
+        <v>0.06164919549820291</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9156987311978873</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0.05367569247165412</v>
+        <v>0.9383508045017971</v>
       </c>
     </row>
     <row r="145">
@@ -3578,19 +3159,16 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1750151769071146</v>
+        <v>0.9697429951367126</v>
       </c>
       <c r="E145" t="n">
-        <v>0.01525414189455118</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.8097306811983342</v>
+        <v>0.03025700486328743</v>
       </c>
     </row>
     <row r="146">
@@ -3600,19 +3178,16 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.03130901244448827</v>
+        <v>0.9999921049689643</v>
       </c>
       <c r="E146" t="n">
-        <v>1.2608074971101e-06</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0.9686897267480147</v>
+        <v>7.895031035763269e-06</v>
       </c>
     </row>
     <row r="147">
@@ -3629,7 +3204,6 @@
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -3638,19 +3212,16 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3307495008073195</v>
+        <v>0.9992201141307785</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0006547838977319431</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0.6685957152949485</v>
+        <v>0.0007798858692215449</v>
       </c>
     </row>
     <row r="149">
@@ -3667,7 +3238,6 @@
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -3683,7 +3253,6 @@
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -3698,13 +3267,10 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.8662200325524702</v>
+        <v>0.9999938152732075</v>
       </c>
       <c r="E151" t="n">
-        <v>8.663076104535597e-06</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.1337713043714253</v>
+        <v>6.184726792447437e-06</v>
       </c>
     </row>
     <row r="152">
@@ -3720,13 +3286,10 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.6399068202122142</v>
+        <v>0.9998562618801007</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0001835166915291545</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.3599096630962565</v>
+        <v>0.0001437381198992629</v>
       </c>
     </row>
     <row r="153">
@@ -3743,7 +3306,6 @@
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -3759,7 +3321,6 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -3775,7 +3336,6 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -3790,13 +3350,10 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1647119440796767</v>
+        <v>0.1431346806768155</v>
       </c>
       <c r="E156" t="n">
-        <v>0.8299411888203123</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.005346867100010985</v>
+        <v>0.8568653193231845</v>
       </c>
     </row>
     <row r="157">
@@ -3813,7 +3370,6 @@
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -3828,13 +3384,10 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.8821472780455736</v>
+        <v>0.9998077232223196</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0002457213910764569</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0.1176070005633499</v>
+        <v>0.0001922767776804378</v>
       </c>
     </row>
     <row r="159">
@@ -3850,13 +3403,10 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9230688002498387</v>
+        <v>0.9999856026041019</v>
       </c>
       <c r="E159" t="n">
-        <v>1.843074073477404e-05</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.07691276900942641</v>
+        <v>1.439739589810663e-05</v>
       </c>
     </row>
     <row r="160">
@@ -3873,7 +3423,6 @@
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -3889,7 +3438,6 @@
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -3905,7 +3453,6 @@
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -3920,13 +3467,10 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0.8858515214248406</v>
+        <v>0.9996568001975953</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0004311723128532418</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0.1137173062623062</v>
+        <v>0.0003431998024047132</v>
       </c>
     </row>
     <row r="164">
@@ -3943,7 +3487,6 @@
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -3959,7 +3502,6 @@
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -3975,7 +3517,6 @@
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -3991,7 +3532,6 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -4007,7 +3547,6 @@
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -4023,7 +3562,6 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -4038,13 +3576,10 @@
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9250821972867058</v>
+        <v>0.9984797193029773</v>
       </c>
       <c r="E170" t="n">
-        <v>0.001737263337737806</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.07318053937555644</v>
+        <v>0.001520280697022683</v>
       </c>
     </row>
     <row r="171">
@@ -4060,13 +3595,10 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.5970384643956311</v>
+        <v>0.9999326498655766</v>
       </c>
       <c r="E171" t="n">
-        <v>8.491876901434087e-05</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.4028766168353544</v>
+        <v>6.73501344233865e-05</v>
       </c>
     </row>
     <row r="172">
@@ -4083,7 +3615,6 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -4092,14 +3623,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -4114,13 +3644,10 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9328800705245174</v>
+        <v>0.9999897249278328</v>
       </c>
       <c r="E174" t="n">
-        <v>1.297367832110229e-05</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.06710695579716143</v>
+        <v>1.027507216724078e-05</v>
       </c>
     </row>
     <row r="175">
@@ -4137,7 +3664,6 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -4153,7 +3679,6 @@
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -4169,7 +3694,6 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -4185,7 +3709,6 @@
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -4201,7 +3724,6 @@
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -4217,7 +3739,6 @@
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -4226,19 +3747,16 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.3566653349093779</v>
+        <v>0.9999994281754256</v>
       </c>
       <c r="E181" t="n">
-        <v>5.946028816416055e-07</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.6433340704877405</v>
+        <v>5.718245744122648e-07</v>
       </c>
     </row>
     <row r="182">
@@ -4254,13 +3772,10 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.8487467705334281</v>
+        <v>0.9999705720738402</v>
       </c>
       <c r="E182" t="n">
-        <v>4.021559259484586e-05</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.1512130138739772</v>
+        <v>2.942792615973333e-05</v>
       </c>
     </row>
     <row r="183">
@@ -4276,13 +3791,10 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.8918352666571223</v>
+        <v>0.9999996782440125</v>
       </c>
       <c r="E183" t="n">
-        <v>4.708202061179506e-07</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.1081642625226715</v>
+        <v>3.217559875038416e-07</v>
       </c>
     </row>
     <row r="184">
@@ -4292,19 +3804,16 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.2849032192177953</v>
+        <v>0.9999287201263656</v>
       </c>
       <c r="E184" t="n">
-        <v>5.701798816328698e-05</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.7150397627940415</v>
+        <v>7.127987363442017e-05</v>
       </c>
     </row>
     <row r="185">
@@ -4320,13 +3829,10 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.7512386554954643</v>
+        <v>0.9999978732716184</v>
       </c>
       <c r="E185" t="n">
-        <v>3.125325585202024e-06</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.2487582191789504</v>
+        <v>2.126728381679304e-06</v>
       </c>
     </row>
     <row r="186">
@@ -4342,13 +3848,10 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.9264153066940232</v>
+        <v>0.9999993973693441</v>
       </c>
       <c r="E186" t="n">
-        <v>8.235158589310479e-07</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.07358386979011797</v>
+        <v>6.026306559574784e-07</v>
       </c>
     </row>
     <row r="187">
@@ -4364,13 +3867,10 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.5386577433298884</v>
+        <v>0.9999988921907721</v>
       </c>
       <c r="E187" t="n">
-        <v>1.457153680476083e-06</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.4613407995164312</v>
+        <v>1.107809227867349e-06</v>
       </c>
     </row>
     <row r="188">
@@ -4386,13 +3886,10 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.7754433254164637</v>
+        <v>0.9999938354531119</v>
       </c>
       <c r="E188" t="n">
-        <v>8.86481207214795e-06</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.2245478097714642</v>
+        <v>6.164546888041099e-06</v>
       </c>
     </row>
     <row r="189">
@@ -4402,19 +3899,16 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3033488623343185</v>
+        <v>0.9999606513544592</v>
       </c>
       <c r="E189" t="n">
-        <v>3.331717065005184e-05</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.6966178204950314</v>
+        <v>3.934864554080237e-05</v>
       </c>
     </row>
     <row r="190">
@@ -4430,13 +3924,10 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0.8491569093888334</v>
+        <v>0.9999910060433639</v>
       </c>
       <c r="E190" t="n">
-        <v>1.26241357882254e-05</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.1508304664753784</v>
+        <v>8.993956636107363e-06</v>
       </c>
     </row>
     <row r="191">
@@ -4453,7 +3944,6 @@
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -4469,7 +3959,6 @@
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -4478,14 +3967,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -4501,7 +3989,6 @@
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -4510,14 +3997,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -4532,13 +4018,10 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.6673339907293451</v>
+        <v>0.9999913778458043</v>
       </c>
       <c r="E196" t="n">
-        <v>1.191906059186927e-05</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.332654090210063</v>
+        <v>8.622154195722508e-06</v>
       </c>
     </row>
     <row r="197">
@@ -4554,13 +4037,10 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.6534180268557699</v>
+        <v>0.9994973988175793</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0006287542893927364</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.3459532188548374</v>
+        <v>0.0005026011824207474</v>
       </c>
     </row>
     <row r="198">
@@ -4577,7 +4057,6 @@
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -4586,14 +4065,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -4602,14 +4080,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -4624,13 +4101,10 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.6290608997212062</v>
+        <v>0.999999990372174</v>
       </c>
       <c r="E201" t="n">
-        <v>1.518739858115891e-08</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.3709390850913953</v>
+        <v>9.627826004250743e-09</v>
       </c>
     </row>
     <row r="202">
@@ -4640,19 +4114,16 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4636487990918709</v>
+        <v>0.9999998413886719</v>
       </c>
       <c r="E202" t="n">
-        <v>2.00386413195155e-07</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0.5363510005217159</v>
+        <v>1.586113280797064e-07</v>
       </c>
     </row>
     <row r="203">
@@ -4662,19 +4133,16 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0.3731537397768602</v>
+        <v>0.9998751838835129</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0001183060752379946</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.6267279541479018</v>
+        <v>0.0001248161164870779</v>
       </c>
     </row>
     <row r="204">
@@ -4690,13 +4158,10 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.5498657828075288</v>
+        <v>0.9848030179881793</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0163843875903735</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.4337498296020977</v>
+        <v>0.01519698201182074</v>
       </c>
     </row>
     <row r="205">
@@ -4712,13 +4177,10 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.0001026410467507044</v>
+        <v>0.0001061551887969747</v>
       </c>
       <c r="E205" t="n">
-        <v>0.9998788642198452</v>
-      </c>
-      <c r="F205" t="n">
-        <v>1.849473340410541e-05</v>
+        <v>0.999893844811203</v>
       </c>
     </row>
     <row r="206">
@@ -4735,7 +4197,6 @@
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -4750,13 +4211,10 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.925012649487187</v>
+        <v>0.9999967096747961</v>
       </c>
       <c r="E207" t="n">
-        <v>4.338836820946377e-06</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0.07498301167599204</v>
+        <v>3.290325203828566e-06</v>
       </c>
     </row>
     <row r="208">
@@ -4772,13 +4230,10 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.8230232450551535</v>
+        <v>0.999999949483775</v>
       </c>
       <c r="E208" t="n">
-        <v>8.059863925032911e-08</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0.1769766743462073</v>
+        <v>5.05162250307012e-08</v>
       </c>
     </row>
     <row r="209">
@@ -4795,7 +4250,6 @@
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -4811,7 +4265,6 @@
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -4827,7 +4280,6 @@
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -4836,14 +4288,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -4859,7 +4310,6 @@
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -4874,13 +4324,10 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.7278527932386668</v>
+        <v>0.9999989309557905</v>
       </c>
       <c r="E214" t="n">
-        <v>1.58753557834912e-06</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.2721456192257548</v>
+        <v>1.069044209457146e-06</v>
       </c>
     </row>
     <row r="215">
@@ -4897,7 +4344,6 @@
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -4913,7 +4359,6 @@
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -4928,13 +4373,10 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.6995725347975249</v>
+        <v>0.9997659836462298</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0003045640775307534</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.3001229011249442</v>
+        <v>0.000234016353770136</v>
       </c>
     </row>
     <row r="218">
@@ -4951,7 +4393,6 @@
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -4967,7 +4408,6 @@
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -4982,13 +4422,10 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>5.296602110553357e-07</v>
+        <v>9.273605414694686e-07</v>
       </c>
       <c r="E220" t="n">
-        <v>0.9999977150427503</v>
-      </c>
-      <c r="F220" t="n">
-        <v>1.755297038704156e-06</v>
+        <v>0.9999990726394585</v>
       </c>
     </row>
     <row r="221">
@@ -5004,13 +4441,10 @@
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.002960483747994712</v>
+        <v>0.00330688959420089</v>
       </c>
       <c r="E221" t="n">
-        <v>0.9965095059090052</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0.0005300103430000799</v>
+        <v>0.9966931104057991</v>
       </c>
     </row>
     <row r="222">
@@ -5026,13 +4460,10 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.6610794687698687</v>
+        <v>0.9963520780223607</v>
       </c>
       <c r="E222" t="n">
-        <v>0.004383918815411954</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.3345366124147194</v>
+        <v>0.003647921977639254</v>
       </c>
     </row>
     <row r="223">
@@ -5048,13 +4479,10 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>4.852741603312393e-07</v>
+        <v>8.721787847498774e-07</v>
       </c>
       <c r="E223" t="n">
-        <v>0.9999976895161604</v>
-      </c>
-      <c r="F223" t="n">
-        <v>1.825209679270932e-06</v>
+        <v>0.9999991278212153</v>
       </c>
     </row>
     <row r="224">
@@ -5064,19 +4492,16 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.291490771216095</v>
+        <v>0.9968637812174057</v>
       </c>
       <c r="E224" t="n">
-        <v>0.002344160658004008</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0.7061650681259011</v>
+        <v>0.003136218782594262</v>
       </c>
     </row>
     <row r="225">
@@ -5092,13 +4517,10 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.7904655689906626</v>
+        <v>0.9999995496270824</v>
       </c>
       <c r="E225" t="n">
-        <v>6.872839329324117e-07</v>
-      </c>
-      <c r="F225" t="n">
-        <v>0.2095337437254045</v>
+        <v>4.503729176043738e-07</v>
       </c>
     </row>
     <row r="226">
@@ -5114,13 +4536,10 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>3.684893781340234e-05</v>
+        <v>5.800615581030844e-05</v>
       </c>
       <c r="E226" t="n">
-        <v>0.9999144941613417</v>
-      </c>
-      <c r="F226" t="n">
-        <v>4.865690084488761e-05</v>
+        <v>0.9999419938441897</v>
       </c>
     </row>
     <row r="227">
@@ -5136,13 +4555,10 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2626971927370817</v>
+        <v>0.2753272855625718</v>
       </c>
       <c r="E227" t="n">
-        <v>0.7169129447731707</v>
-      </c>
-      <c r="F227" t="n">
-        <v>0.02038986248974747</v>
+        <v>0.7246727144374282</v>
       </c>
     </row>
     <row r="228">
@@ -5158,13 +4574,10 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.6822909870262606</v>
+        <v>0.8095068542021033</v>
       </c>
       <c r="E228" t="n">
-        <v>0.2066471745566177</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.1110618384171219</v>
+        <v>0.1904931457978966</v>
       </c>
     </row>
     <row r="229">
@@ -5180,13 +4593,10 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>7.103659129832869e-06</v>
+        <v>2.705686190307421e-05</v>
       </c>
       <c r="E229" t="n">
-        <v>0.9994072050815362</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0.0005856912593337919</v>
+        <v>0.9999729431380969</v>
       </c>
     </row>
     <row r="230">
@@ -5202,13 +4612,10 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.9698267687108909</v>
+        <v>0.9999998759677828</v>
       </c>
       <c r="E230" t="n">
-        <v>1.499661598166255e-07</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0.03017308132294923</v>
+        <v>1.240322171586393e-07</v>
       </c>
     </row>
     <row r="231">
@@ -5224,13 +4631,10 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.9518154402412357</v>
+        <v>0.9999995375382074</v>
       </c>
       <c r="E231" t="n">
-        <v>5.921755442533409e-07</v>
-      </c>
-      <c r="F231" t="n">
-        <v>0.04818396758322003</v>
+        <v>4.624617926037675e-07</v>
       </c>
     </row>
     <row r="232">
@@ -5246,13 +4650,10 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.7707418512818381</v>
+        <v>0.9208684146835484</v>
       </c>
       <c r="E232" t="n">
-        <v>0.08931768902685222</v>
-      </c>
-      <c r="F232" t="n">
-        <v>0.1399404596913096</v>
+        <v>0.07913158531645162</v>
       </c>
     </row>
     <row r="233">
@@ -5268,13 +4669,10 @@
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.01689114076184105</v>
+        <v>0.01299040667417606</v>
       </c>
       <c r="E233" t="n">
-        <v>0.9826460422843394</v>
-      </c>
-      <c r="F233" t="n">
-        <v>0.0004628169538197034</v>
+        <v>0.9870095933258239</v>
       </c>
     </row>
     <row r="234">
@@ -5290,13 +4688,10 @@
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0.8262462257657064</v>
+        <v>0.9999973670916658</v>
       </c>
       <c r="E234" t="n">
-        <v>3.836171931306519e-06</v>
-      </c>
-      <c r="F234" t="n">
-        <v>0.1737499380623624</v>
+        <v>2.632908334202288e-06</v>
       </c>
     </row>
     <row r="235">
@@ -5312,13 +4707,10 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0.7257479922842491</v>
+        <v>0.9999743748481901</v>
       </c>
       <c r="E235" t="n">
-        <v>3.538195254706627e-05</v>
-      </c>
-      <c r="F235" t="n">
-        <v>0.2742166257632038</v>
+        <v>2.562515180990684e-05</v>
       </c>
     </row>
     <row r="236">
@@ -5328,19 +4720,16 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.345629176966588</v>
+        <v>0.9992404541055629</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0006571929960198206</v>
-      </c>
-      <c r="F236" t="n">
-        <v>0.6537136300373921</v>
+        <v>0.0007595458944370133</v>
       </c>
     </row>
     <row r="237">
@@ -5356,19 +4745,16 @@
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.5763295410124705</v>
+        <v>0.999998733897256</v>
       </c>
       <c r="E237" t="n">
-        <v>1.718295290090401e-06</v>
-      </c>
-      <c r="F237" t="n">
-        <v>0.4236687406922394</v>
+        <v>1.266102744004618e-06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/03_LDA_Classification/artifacts/03_updated_data.xlsx
+++ b/results/03_LDA_Classification/artifacts/03_updated_data.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:F237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,7 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -477,6 +478,7 @@
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr"/>
@@ -500,6 +502,11 @@
           <t>Prob_Cluster 2</t>
         </is>
       </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Prob_Cluster 3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -515,16 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9994370294159177</v>
+        <v>0.06695308702691306</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0005629705840822543</v>
+        <v>0.5715465427347223</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3615003702383646</v>
       </c>
     </row>
     <row r="6">
@@ -534,13 +544,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -549,16 +560,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999857834570037</v>
+        <v>0.0841684166524419</v>
       </c>
       <c r="E7" t="n">
-        <v>1.421654299628306e-05</v>
+        <v>0.005515498754773819</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9103160845927843</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +582,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999741222957295</v>
+        <v>0.09122081767763607</v>
       </c>
       <c r="E8" t="n">
-        <v>2.587770427055703e-05</v>
+        <v>0.1912783125643355</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7175008697580284</v>
       </c>
     </row>
     <row r="9">
@@ -587,16 +604,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999745210199439</v>
+        <v>0.2336917901229157</v>
       </c>
       <c r="E9" t="n">
-        <v>2.547898005608538e-05</v>
+        <v>0.1555295932597322</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.610778616617352</v>
       </c>
     </row>
     <row r="10">
@@ -606,16 +626,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999902171225376</v>
+        <v>0.1163045175621975</v>
       </c>
       <c r="E10" t="n">
-        <v>9.782877462504263e-06</v>
+        <v>0.05217910496053632</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8315163774772661</v>
       </c>
     </row>
     <row r="11">
@@ -625,17 +648,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9996390615041485</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0003609384958515414</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -644,17 +664,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9999842688420607</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.573115793929459e-05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -663,16 +680,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999994993492154</v>
+        <v>0.3950453550899977</v>
       </c>
       <c r="E13" t="n">
-        <v>5.006507845997768e-07</v>
+        <v>0.001907177603145528</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6030474673068569</v>
       </c>
     </row>
     <row r="14">
@@ -682,16 +702,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999959904296857</v>
+        <v>0.2686867124850299</v>
       </c>
       <c r="E14" t="n">
-        <v>4.009570314327864e-06</v>
+        <v>0.0006998771461610526</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.730613410368809</v>
       </c>
     </row>
     <row r="15">
@@ -707,10 +730,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999618477409998</v>
+        <v>0.3649051996932342</v>
       </c>
       <c r="E15" t="n">
-        <v>3.815225900021037e-05</v>
+        <v>0.3221421570562781</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3129526432504878</v>
       </c>
     </row>
     <row r="16">
@@ -720,16 +746,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9992937713673032</v>
+        <v>0.394609279822275</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0007062286326967538</v>
+        <v>0.1536157943690066</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4517749258087183</v>
       </c>
     </row>
     <row r="17">
@@ -739,16 +768,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999763167261023</v>
+        <v>0.09757135332978835</v>
       </c>
       <c r="E17" t="n">
-        <v>2.368327389768836e-05</v>
+        <v>0.001360643948872727</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9010680027213389</v>
       </c>
     </row>
     <row r="18">
@@ -758,16 +790,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999965441635336</v>
+        <v>0.2918695183211681</v>
       </c>
       <c r="E18" t="n">
-        <v>3.455836466437804e-06</v>
+        <v>0.004154867703820697</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7039756139750113</v>
       </c>
     </row>
     <row r="19">
@@ -777,17 +812,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.9438582884224705</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.05614171157752942</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -796,16 +828,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999924551840922</v>
+        <v>0.1530217476088234</v>
       </c>
       <c r="E20" t="n">
-        <v>7.544815907780561e-06</v>
+        <v>0.003527045393228606</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.843451206997948</v>
       </c>
     </row>
     <row r="21">
@@ -815,16 +850,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6149291386146059</v>
+        <v>0.004745467912706987</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3850708613853942</v>
+        <v>0.9913970830617775</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.003857449025515514</v>
       </c>
     </row>
     <row r="22">
@@ -834,16 +872,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999718695998208</v>
+        <v>0.04680930656414131</v>
       </c>
       <c r="E22" t="n">
-        <v>2.813040017928032e-05</v>
+        <v>0.8588068778084125</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.09438381562744634</v>
       </c>
     </row>
     <row r="23">
@@ -853,16 +894,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999992072475127</v>
+        <v>0.06606947325426879</v>
       </c>
       <c r="E23" t="n">
-        <v>7.927524873708793e-07</v>
+        <v>0.0004509685762483036</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9334795581694829</v>
       </c>
     </row>
     <row r="24">
@@ -872,16 +916,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9864138737364927</v>
+        <v>0.3619653234965713</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01358612626350729</v>
+        <v>0.08324734284413243</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5547873336592962</v>
       </c>
     </row>
     <row r="25">
@@ -891,16 +938,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999998687132159</v>
+        <v>0.03922642250897136</v>
       </c>
       <c r="E25" t="n">
-        <v>1.312867840678461e-07</v>
+        <v>3.741097835443816e-05</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9607361665126741</v>
       </c>
     </row>
     <row r="26">
@@ -910,17 +960,14 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.5662348078346129</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.4337651921653872</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -929,16 +976,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9999999930038727</v>
+        <v>0.006271092346387379</v>
       </c>
       <c r="E27" t="n">
-        <v>6.996127367399476e-09</v>
+        <v>0.9255690165652756</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.06815989108833719</v>
       </c>
     </row>
     <row r="28">
@@ -948,16 +998,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9999779006811235</v>
+        <v>0.01274280037513032</v>
       </c>
       <c r="E28" t="n">
-        <v>2.209931887653501e-05</v>
+        <v>0.9476706964965973</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.03958650312827233</v>
       </c>
     </row>
     <row r="29">
@@ -967,17 +1020,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.9928472672716435</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.00715273272835645</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -992,10 +1042,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2.463383265149943e-07</v>
+        <v>0.0001936149711999758</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9999997536616735</v>
+        <v>0.9986175767755995</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.001188808253200593</v>
       </c>
     </row>
     <row r="31">
@@ -1005,17 +1058,14 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.9994021114908841</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.000597888509115896</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1030,10 +1080,13 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.01764108258382</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.8539426430667966</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1284162743493836</v>
       </c>
     </row>
     <row r="33">
@@ -1046,14 +1099,11 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.270204973482294e-08</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.9999999672979503</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1062,17 +1112,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.9999397647106637</v>
-      </c>
-      <c r="E34" t="n">
-        <v>6.023528933634769e-05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1081,16 +1128,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9833197826682381</v>
+        <v>0.01461224928266128</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01668021733176197</v>
+        <v>0.9743144189969705</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0110733317203684</v>
       </c>
     </row>
     <row r="36">
@@ -1100,16 +1150,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.330913157460145e-11</v>
+        <v>0.02117469497472989</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9999999999866909</v>
+        <v>0.0001722574382694238</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9786530475870008</v>
       </c>
     </row>
     <row r="37">
@@ -1119,17 +1172,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.6888056619438209</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.3111943380561791</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1138,16 +1188,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9999996426562661</v>
+        <v>0.04861013418036564</v>
       </c>
       <c r="E38" t="n">
-        <v>3.573437339069683e-07</v>
+        <v>0.001814819528907327</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9495750462907271</v>
       </c>
     </row>
     <row r="39">
@@ -1157,16 +1210,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9996345238959438</v>
+        <v>0.02771371917155769</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0003654761040562116</v>
+        <v>0.0002950434994754487</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.971991237328967</v>
       </c>
     </row>
     <row r="40">
@@ -1176,16 +1232,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9953528749922381</v>
+        <v>0.00518169452611572</v>
       </c>
       <c r="E40" t="n">
-        <v>0.004647125007761838</v>
+        <v>0.9630619830712444</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.03175632240263999</v>
       </c>
     </row>
     <row r="41">
@@ -1195,16 +1254,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9999957324607841</v>
+        <v>0.01149344269244985</v>
       </c>
       <c r="E41" t="n">
-        <v>4.267539215905691e-06</v>
+        <v>0.9689864381796881</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.01952011912786206</v>
       </c>
     </row>
     <row r="42">
@@ -1220,10 +1282,13 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.003147783727003306</v>
+        <v>0.0006838422350959914</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9968522162729967</v>
+        <v>0.9951834084992324</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.004132749265671674</v>
       </c>
     </row>
     <row r="43">
@@ -1233,16 +1298,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.761256345795715e-08</v>
+        <v>0.08706757906626354</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9999999723874365</v>
+        <v>0.1575660605451472</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7553663603885892</v>
       </c>
     </row>
     <row r="44">
@@ -1252,16 +1320,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9999883054126635</v>
+        <v>0.05325202159567882</v>
       </c>
       <c r="E44" t="n">
-        <v>1.169458733648802e-05</v>
+        <v>0.03068796834140378</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.9160600100629174</v>
       </c>
     </row>
     <row r="45">
@@ -1271,16 +1342,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9456638320097462</v>
+        <v>0.002522395833924441</v>
       </c>
       <c r="E45" t="n">
-        <v>0.05433616799025372</v>
+        <v>0.9942064786953841</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.003271125470691285</v>
       </c>
     </row>
     <row r="46">
@@ -1290,16 +1364,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9902985946765539</v>
+        <v>0.009791120527104114</v>
       </c>
       <c r="E46" t="n">
-        <v>0.009701405323446105</v>
+        <v>0.9638600996244823</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.02634877984841374</v>
       </c>
     </row>
     <row r="47">
@@ -1309,17 +1386,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.9999992613169872</v>
-      </c>
-      <c r="E47" t="n">
-        <v>7.386830127213638e-07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1328,16 +1402,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9999999957735648</v>
+        <v>0.02847175308125886</v>
       </c>
       <c r="E48" t="n">
-        <v>4.226435223288692e-09</v>
+        <v>0.0001254677408195925</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9714027791779216</v>
       </c>
     </row>
     <row r="49">
@@ -1347,17 +1424,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9852124293345479</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.01478757066545206</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1366,17 +1440,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.3899123167824377</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.6100876832175623</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1385,17 +1456,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.9999993763333088</v>
-      </c>
-      <c r="E51" t="n">
-        <v>6.236666912014923e-07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1404,17 +1472,14 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.9998795740465153</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.0001204259534847385</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1423,16 +1488,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9982271040127696</v>
+        <v>0.07988659772505412</v>
       </c>
       <c r="E53" t="n">
-        <v>0.001772895987230412</v>
+        <v>0.0001094457791527386</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.9200039564957933</v>
       </c>
     </row>
     <row r="54">
@@ -1442,17 +1510,14 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.9998612853304305</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0001387146695694419</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1461,16 +1526,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9960077573652154</v>
+        <v>0.1921410566193744</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003992242634784542</v>
+        <v>0.0002055128105619063</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8076534305700638</v>
       </c>
     </row>
     <row r="56">
@@ -1480,16 +1548,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9988983167485165</v>
+        <v>0.08266301622245328</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001101683251483495</v>
+        <v>7.181856802231367e-05</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.9172651652095244</v>
       </c>
     </row>
     <row r="57">
@@ -1502,14 +1573,11 @@
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.0484273128490893</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.9515726871509107</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1518,16 +1586,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9999676382796191</v>
+        <v>0.3716251933257147</v>
       </c>
       <c r="E58" t="n">
-        <v>3.236172038091091e-05</v>
+        <v>0.002445900699352102</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.6259289059749331</v>
       </c>
     </row>
     <row r="59">
@@ -1540,14 +1611,11 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.9840957376352911</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.01590426236470893</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1556,16 +1624,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4529492582960561</v>
+        <v>0.2136520868680377</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5470507417039439</v>
+        <v>0.0009278810417173648</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.785420032090245</v>
       </c>
     </row>
     <row r="61">
@@ -1575,13 +1646,20 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3618771748013579</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.09091707637906467</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5472057488195773</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1590,16 +1668,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.08165278453545599</v>
+        <v>0.2367800497205097</v>
       </c>
       <c r="E62" t="n">
-        <v>0.918347215464544</v>
+        <v>0.001464007657267312</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.761755942622223</v>
       </c>
     </row>
     <row r="63">
@@ -1609,17 +1690,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.7083137603173533</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.2916862396826468</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1628,16 +1706,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0.999978960664349</v>
+        <v>0.3537424737117161</v>
       </c>
       <c r="E64" t="n">
-        <v>2.103933565105146e-05</v>
+        <v>0.001760258361820348</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.6444972679264636</v>
       </c>
     </row>
     <row r="65">
@@ -1647,16 +1728,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5816233976978904</v>
+        <v>0.03998973149201641</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4183766023021095</v>
+        <v>1.176957873208254e-05</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.9599984989292515</v>
       </c>
     </row>
     <row r="66">
@@ -1666,16 +1750,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.999978613703595</v>
+        <v>0.03681144211126526</v>
       </c>
       <c r="E66" t="n">
-        <v>2.13862964049752e-05</v>
+        <v>2.153486585683547e-05</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.9631670230228779</v>
       </c>
     </row>
     <row r="67">
@@ -1685,16 +1772,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9992515018709702</v>
+        <v>0.1275082535587901</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0007484981290298248</v>
+        <v>0.009976823140131456</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.8625149233010785</v>
       </c>
     </row>
     <row r="68">
@@ -1704,16 +1794,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9998643665634882</v>
+        <v>0.01446230034249507</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0001356334365118155</v>
+        <v>0.0001672890836758065</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.9853704105738292</v>
       </c>
     </row>
     <row r="69">
@@ -1723,16 +1816,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9493563868868471</v>
+        <v>0.007271678733250411</v>
       </c>
       <c r="E69" t="n">
-        <v>0.05064361311315295</v>
+        <v>0.9649432827198416</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.02778503854690804</v>
       </c>
     </row>
     <row r="70">
@@ -1742,16 +1838,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9999492101956737</v>
+        <v>0.02424224490177412</v>
       </c>
       <c r="E70" t="n">
-        <v>5.078980432629481e-05</v>
+        <v>0.0003754040513191101</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.9753823510469068</v>
       </c>
     </row>
     <row r="71">
@@ -1761,16 +1860,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9999977778324606</v>
+        <v>0.03240448864784092</v>
       </c>
       <c r="E71" t="n">
-        <v>2.222167539425228e-06</v>
+        <v>0.00188526108233102</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.9657102502698282</v>
       </c>
     </row>
     <row r="72">
@@ -1780,16 +1882,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9999969033545016</v>
+        <v>0.03443252459847098</v>
       </c>
       <c r="E72" t="n">
-        <v>3.096645498381546e-06</v>
+        <v>0.002213952394937282</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.9633535230065918</v>
       </c>
     </row>
     <row r="73">
@@ -1799,16 +1904,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.6563552684720735</v>
+        <v>0.007521878142096548</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3436447315279265</v>
+        <v>0.9819438419542718</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0105342799036316</v>
       </c>
     </row>
     <row r="74">
@@ -1818,16 +1926,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9959833556379938</v>
+        <v>0.01665934354285173</v>
       </c>
       <c r="E74" t="n">
-        <v>0.004016644362006175</v>
+        <v>0.0002156676277106155</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9831249888294377</v>
       </c>
     </row>
     <row r="75">
@@ -1837,16 +1948,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9975055905634014</v>
+        <v>0.0005709816073634709</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00249440943659861</v>
+        <v>0.9991654531963369</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.0002635651962997639</v>
       </c>
     </row>
     <row r="76">
@@ -1856,16 +1970,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.002779264079736388</v>
+        <v>0.04083894918333976</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9972207359202636</v>
+        <v>0.0005832913275063671</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.9585777594891538</v>
       </c>
     </row>
     <row r="77">
@@ -1875,16 +1992,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9999939866372628</v>
+        <v>0.05048200343904631</v>
       </c>
       <c r="E77" t="n">
-        <v>6.013362737230287e-06</v>
+        <v>0.001723942051378401</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.9477940545095753</v>
       </c>
     </row>
     <row r="78">
@@ -1900,10 +2020,13 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9999137354397027</v>
+        <v>0.4257262756963475</v>
       </c>
       <c r="E78" t="n">
-        <v>8.6264560297234e-05</v>
+        <v>0.2713008846581093</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.3029728396455432</v>
       </c>
     </row>
     <row r="79">
@@ -1913,17 +2036,14 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.9994082542556327</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.0005917457443672268</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1932,16 +2052,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9999999333377995</v>
+        <v>0.05257453113470845</v>
       </c>
       <c r="E80" t="n">
-        <v>6.666220056203019e-08</v>
+        <v>0.0007988355930389492</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9466266332722526</v>
       </c>
     </row>
     <row r="81">
@@ -1951,16 +2074,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9999984460096433</v>
+        <v>0.02853796499073681</v>
       </c>
       <c r="E81" t="n">
-        <v>1.553990356734324e-06</v>
+        <v>0.0003989832567724986</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.9710630517524907</v>
       </c>
     </row>
     <row r="82">
@@ -1970,17 +2096,14 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.994667596815629</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.00533240318437095</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1989,17 +2112,14 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.9999949218310719</v>
-      </c>
-      <c r="E83" t="n">
-        <v>5.078168928134574e-06</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -2008,16 +2128,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9935697432487105</v>
+        <v>0.03909978434421604</v>
       </c>
       <c r="E84" t="n">
-        <v>0.006430256751289528</v>
+        <v>0.000846685403808488</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.9600535302519755</v>
       </c>
     </row>
     <row r="85">
@@ -2027,16 +2150,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9999980543417524</v>
+        <v>0.0396591028660729</v>
       </c>
       <c r="E85" t="n">
-        <v>1.945658247597983e-06</v>
+        <v>0.001426987558237867</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.9589139095756893</v>
       </c>
     </row>
     <row r="86">
@@ -2046,16 +2172,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8807366740548866</v>
+        <v>0.03797523123112864</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1192633259451134</v>
+        <v>0.0001482772429015036</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.9618764915259698</v>
       </c>
     </row>
     <row r="87">
@@ -2065,16 +2194,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9998052421714775</v>
+        <v>0.1501386521012233</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0001947578285224935</v>
+        <v>0.01314722027819746</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.8367141276205792</v>
       </c>
     </row>
     <row r="88">
@@ -2084,16 +2216,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9999996954282625</v>
+        <v>0.05043388773566827</v>
       </c>
       <c r="E88" t="n">
-        <v>3.045717374427348e-07</v>
+        <v>0.001481104405004217</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.9480850078593275</v>
       </c>
     </row>
     <row r="89">
@@ -2103,16 +2238,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9984010567424756</v>
+        <v>0.2121459833595742</v>
       </c>
       <c r="E89" t="n">
-        <v>0.001598943257524389</v>
+        <v>0.1190284388114725</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.6688255778289532</v>
       </c>
     </row>
     <row r="90">
@@ -2122,16 +2260,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9998784640792086</v>
+        <v>0.04570070538402787</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0001215359207914966</v>
+        <v>0.0001435547481787413</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.9541557398677933</v>
       </c>
     </row>
     <row r="91">
@@ -2141,16 +2282,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9999999197082675</v>
+        <v>0.1344076960923999</v>
       </c>
       <c r="E91" t="n">
-        <v>8.029173244055565e-08</v>
+        <v>0.001024088632523507</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.8645682152750765</v>
       </c>
     </row>
     <row r="92">
@@ -2160,16 +2304,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9998264672537391</v>
+        <v>0.06030869799916322</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0001735327462608492</v>
+        <v>0.0001301083155552314</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.9395611936852816</v>
       </c>
     </row>
     <row r="93">
@@ -2179,16 +2326,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.8879388280439396</v>
+        <v>0.09226256908064959</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1120611719560604</v>
+        <v>0.0001919493760726727</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.9075454815432776</v>
       </c>
     </row>
     <row r="94">
@@ -2201,14 +2351,11 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.9999789974092727</v>
-      </c>
-      <c r="E94" t="n">
-        <v>2.100259072735807e-05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2217,17 +2364,14 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0.9999991311123034</v>
-      </c>
-      <c r="E95" t="n">
-        <v>8.688876965758181e-07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -2236,16 +2380,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9957045797546025</v>
+        <v>0.1427367791720744</v>
       </c>
       <c r="E96" t="n">
-        <v>0.004295420245397507</v>
+        <v>0.03211900277071633</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.8251442180572093</v>
       </c>
     </row>
     <row r="97">
@@ -2255,16 +2402,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9975639072324957</v>
+        <v>0.1317496972397931</v>
       </c>
       <c r="E97" t="n">
-        <v>0.002436092767504325</v>
+        <v>0.02453880589854039</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.8437114968616665</v>
       </c>
     </row>
     <row r="98">
@@ -2274,16 +2424,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.999970097023432</v>
+        <v>0.1566553709238436</v>
       </c>
       <c r="E98" t="n">
-        <v>2.990297656806216e-05</v>
+        <v>0.0005293454074513534</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.8428152836687051</v>
       </c>
     </row>
     <row r="99">
@@ -2293,16 +2446,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9974044074860996</v>
+        <v>0.1459031391524146</v>
       </c>
       <c r="E99" t="n">
-        <v>0.002595592513900376</v>
+        <v>0.01107281065870517</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.8430240501888802</v>
       </c>
     </row>
     <row r="100">
@@ -2312,16 +2468,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0.888207831180719</v>
+        <v>0.1759581128524564</v>
       </c>
       <c r="E100" t="n">
-        <v>0.111792168819281</v>
+        <v>0.0626865149828518</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.7613553721646917</v>
       </c>
     </row>
     <row r="101">
@@ -2331,16 +2490,19 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.09404589050175716</v>
+        <v>0.1647694580201686</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9059541094982428</v>
+        <v>0.08631377329991669</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.7489167686799147</v>
       </c>
     </row>
     <row r="102">
@@ -2350,16 +2512,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9999984942229337</v>
+        <v>0.06289362872391292</v>
       </c>
       <c r="E102" t="n">
-        <v>1.505777066246886e-06</v>
+        <v>0.0004746110827176283</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.9366317601933695</v>
       </c>
     </row>
     <row r="103">
@@ -2369,17 +2534,14 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0.9917074974656341</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0.008292502534365843</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -2388,13 +2550,14 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2403,16 +2566,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.8244063688773521</v>
+        <v>0.04467602773391886</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1755936311226479</v>
+        <v>0.006133182909872634</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.9491907893562085</v>
       </c>
     </row>
     <row r="106">
@@ -2422,16 +2588,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9945521413852751</v>
+        <v>0.06146763576824115</v>
       </c>
       <c r="E106" t="n">
-        <v>0.005447858614724835</v>
+        <v>0.007666187822415195</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.9308661764093437</v>
       </c>
     </row>
     <row r="107">
@@ -2441,17 +2610,14 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0.9999111955376657</v>
-      </c>
-      <c r="E107" t="n">
-        <v>8.880446233428549e-05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -2460,16 +2626,19 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9999997876638032</v>
+        <v>0.1069448106857069</v>
       </c>
       <c r="E108" t="n">
-        <v>2.123361968122701e-07</v>
+        <v>0.001641347579765584</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.8914138417345275</v>
       </c>
     </row>
     <row r="109">
@@ -2479,16 +2648,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9999704233875857</v>
+        <v>0.0670634929288202</v>
       </c>
       <c r="E109" t="n">
-        <v>2.95766124142816e-05</v>
+        <v>0.00322410935209534</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.9297123977190844</v>
       </c>
     </row>
     <row r="110">
@@ -2498,16 +2670,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9999978193764207</v>
+        <v>0.1420321093598723</v>
       </c>
       <c r="E110" t="n">
-        <v>2.180623579252055e-06</v>
+        <v>0.0008244029457555915</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.8571434876943722</v>
       </c>
     </row>
     <row r="111">
@@ -2517,16 +2692,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9996262225163777</v>
+        <v>0.2674305137235486</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0003737774836223772</v>
+        <v>0.04054023194752293</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.6920292543289285</v>
       </c>
     </row>
     <row r="112">
@@ -2536,16 +2714,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9995397724331357</v>
+        <v>0.1501099750758209</v>
       </c>
       <c r="E112" t="n">
-        <v>0.00046022756686425</v>
+        <v>0.001317350033555178</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.8485726748906239</v>
       </c>
     </row>
     <row r="113">
@@ -2555,16 +2736,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9970459267842873</v>
+        <v>0.1578500333474016</v>
       </c>
       <c r="E113" t="n">
-        <v>0.002954073215712733</v>
+        <v>0.003622851091929817</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.8385271155606686</v>
       </c>
     </row>
     <row r="114">
@@ -2574,16 +2758,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9999679368733725</v>
+        <v>0.1120627326308315</v>
       </c>
       <c r="E114" t="n">
-        <v>3.206312662751521e-05</v>
+        <v>0.01059342056879852</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.87734384680037</v>
       </c>
     </row>
     <row r="115">
@@ -2596,14 +2783,11 @@
         <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0.9999336086788486</v>
-      </c>
-      <c r="E115" t="n">
-        <v>6.639132115133908e-05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -2612,16 +2796,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9998591708578187</v>
+        <v>0.214003022994158</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0001408291421812583</v>
+        <v>0.004374013172985871</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.7816229638328561</v>
       </c>
     </row>
     <row r="117">
@@ -2631,16 +2818,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9997162286102887</v>
+        <v>0.1251714934636673</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0002837713897112502</v>
+        <v>0.001106608483916975</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8737218980524156</v>
       </c>
     </row>
     <row r="118">
@@ -2656,10 +2846,13 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9990584684734629</v>
+        <v>0.509884008332356</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0009415315265371031</v>
+        <v>0.004463149399185897</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.4856528422684581</v>
       </c>
     </row>
     <row r="119">
@@ -2675,10 +2868,13 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9999995443412794</v>
+        <v>0.7415979851083691</v>
       </c>
       <c r="E119" t="n">
-        <v>4.556587206896692e-07</v>
+        <v>0.002595437303708902</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.255806577587922</v>
       </c>
     </row>
     <row r="120">
@@ -2688,16 +2884,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9999812175178842</v>
+        <v>0.2176020484592271</v>
       </c>
       <c r="E120" t="n">
-        <v>1.878248211584606e-05</v>
+        <v>0.002029254322340889</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.7803686972184319</v>
       </c>
     </row>
     <row r="121">
@@ -2707,17 +2906,14 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0.9999575497692472</v>
-      </c>
-      <c r="E121" t="n">
-        <v>4.245023075272756e-05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2726,16 +2922,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9999991173541274</v>
+        <v>0.2047931147598669</v>
       </c>
       <c r="E122" t="n">
-        <v>8.826458726032282e-07</v>
+        <v>0.005271326428005031</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.7899355588121281</v>
       </c>
     </row>
     <row r="123">
@@ -2748,14 +2947,11 @@
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0.9937536499743952</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0.006246350025604838</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2764,16 +2960,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9999677106729249</v>
+        <v>0.1467584516340697</v>
       </c>
       <c r="E124" t="n">
-        <v>3.228932707506022e-05</v>
+        <v>0.0009122732889453034</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.852329275076985</v>
       </c>
     </row>
     <row r="125">
@@ -2783,16 +2982,19 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9999948081240377</v>
+        <v>0.1791173455329138</v>
       </c>
       <c r="E125" t="n">
-        <v>5.191875962310331e-06</v>
+        <v>0.006249385181398419</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.8146332692856878</v>
       </c>
     </row>
     <row r="126">
@@ -2802,16 +3004,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9977518417234348</v>
+        <v>0.2045284261637411</v>
       </c>
       <c r="E126" t="n">
-        <v>0.002248158276565214</v>
+        <v>0.01913190897542324</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7763396648608357</v>
       </c>
     </row>
     <row r="127">
@@ -2821,16 +3026,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9818037222424594</v>
+        <v>0.2217255558032814</v>
       </c>
       <c r="E127" t="n">
-        <v>0.01819627775754061</v>
+        <v>0.01706999965017226</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.7612044445465462</v>
       </c>
     </row>
     <row r="128">
@@ -2840,16 +3048,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4679654807145243</v>
+        <v>0.131431707791041</v>
       </c>
       <c r="E128" t="n">
-        <v>0.5320345192854757</v>
+        <v>0.002213065582006594</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.8663552266269523</v>
       </c>
     </row>
     <row r="129">
@@ -2859,16 +3070,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>5.515210886430921e-06</v>
+        <v>0.06700748191670199</v>
       </c>
       <c r="E129" t="n">
-        <v>0.9999944847891136</v>
+        <v>6.70754045241905e-06</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.9329858105428456</v>
       </c>
     </row>
     <row r="130">
@@ -2878,16 +3092,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9944598476726647</v>
+        <v>0.3034887506063946</v>
       </c>
       <c r="E130" t="n">
-        <v>0.005540152327335258</v>
+        <v>0.04065835057389507</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6558528988197104</v>
       </c>
     </row>
     <row r="131">
@@ -2897,16 +3114,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9999994308185277</v>
+        <v>0.1569575900231417</v>
       </c>
       <c r="E131" t="n">
-        <v>5.691814722406058e-07</v>
+        <v>0.00029085105579659</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.8427515589210617</v>
       </c>
     </row>
     <row r="132">
@@ -2919,14 +3139,11 @@
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="n">
-        <v>0.9285780847040511</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0.07142191529594891</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -2935,16 +3152,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9999688834333027</v>
+        <v>0.1523016670344886</v>
       </c>
       <c r="E133" t="n">
-        <v>3.111656669727785e-05</v>
+        <v>0.00189525552618502</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8458030774393265</v>
       </c>
     </row>
     <row r="134">
@@ -2954,16 +3174,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9999951612007786</v>
+        <v>0.1687522732483856</v>
       </c>
       <c r="E134" t="n">
-        <v>4.838799221469469e-06</v>
+        <v>0.004140482443384708</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.8271072443082298</v>
       </c>
     </row>
     <row r="135">
@@ -2973,16 +3196,19 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9999352164299828</v>
+        <v>0.1319615922783115</v>
       </c>
       <c r="E135" t="n">
-        <v>6.478357001711383e-05</v>
+        <v>0.002163421791610571</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.8658749859300781</v>
       </c>
     </row>
     <row r="136">
@@ -2992,16 +3218,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9999095410985065</v>
+        <v>0.3149027506083431</v>
       </c>
       <c r="E136" t="n">
-        <v>9.045890149351691e-05</v>
+        <v>0.006115004757815034</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.6789822446338419</v>
       </c>
     </row>
     <row r="137">
@@ -3011,16 +3240,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1336991829718509</v>
+        <v>0.09393270521473908</v>
       </c>
       <c r="E137" t="n">
-        <v>0.8663008170281491</v>
+        <v>0.0005335874104918796</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.9055337073747691</v>
       </c>
     </row>
     <row r="138">
@@ -3033,10 +3265,17 @@
         <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.1163449494784465</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.7656966361200997</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.1179584144014537</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -3045,16 +3284,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9999915454673454</v>
+        <v>0.3263061161304868</v>
       </c>
       <c r="E139" t="n">
-        <v>8.454532654687614e-06</v>
+        <v>0.008416034679883453</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6652778491896296</v>
       </c>
     </row>
     <row r="140">
@@ -3064,16 +3306,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.9999948081943347</v>
+        <v>0.1330384237812589</v>
       </c>
       <c r="E140" t="n">
-        <v>5.191805665282046e-06</v>
+        <v>0.06215262118707515</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.8048089550316661</v>
       </c>
     </row>
     <row r="141">
@@ -3083,16 +3328,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9974487849824101</v>
+        <v>0.1128501284125811</v>
       </c>
       <c r="E141" t="n">
-        <v>0.002551215017589953</v>
+        <v>0.0004541582086737358</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.8866957133787451</v>
       </c>
     </row>
     <row r="142">
@@ -3102,16 +3350,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9999902175456775</v>
+        <v>0.3367407044624582</v>
       </c>
       <c r="E142" t="n">
-        <v>9.782454322526081e-06</v>
+        <v>0.01008295651195576</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6531763390255861</v>
       </c>
     </row>
     <row r="143">
@@ -3121,16 +3372,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.999996546289818</v>
+        <v>0.2052919024587025</v>
       </c>
       <c r="E143" t="n">
-        <v>3.453710182004945e-06</v>
+        <v>0.00184133378367973</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.7928667637576178</v>
       </c>
     </row>
     <row r="144">
@@ -3140,16 +3394,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.06164919549820291</v>
+        <v>0.3761160677969747</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9383508045017971</v>
+        <v>7.477396826527639e-05</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.6238091582347601</v>
       </c>
     </row>
     <row r="145">
@@ -3159,16 +3416,19 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9697429951367126</v>
+        <v>0.1217782060015587</v>
       </c>
       <c r="E145" t="n">
-        <v>0.03025700486328743</v>
+        <v>0.0003221598585572634</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.8778996341398841</v>
       </c>
     </row>
     <row r="146">
@@ -3178,16 +3438,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9999921049689643</v>
+        <v>0.3594399865833877</v>
       </c>
       <c r="E146" t="n">
-        <v>7.895031035763269e-06</v>
+        <v>0.2555693062951506</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.3849907071214617</v>
       </c>
     </row>
     <row r="147">
@@ -3197,13 +3460,14 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -3212,16 +3476,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9992201141307785</v>
+        <v>0.1395557700078211</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0007798858692215449</v>
+        <v>0.0004061443414031415</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.8600380856507758</v>
       </c>
     </row>
     <row r="149">
@@ -3231,13 +3498,20 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.4205157687694834</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.06189578027670663</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.51758845095381</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -3246,13 +3520,20 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.1820920674802546</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.003088946095086342</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.8148189864246591</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -3261,16 +3542,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9999938152732075</v>
+        <v>0.1529336401878333</v>
       </c>
       <c r="E151" t="n">
-        <v>6.184726792447437e-06</v>
+        <v>0.004230640360618126</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.8428357194515487</v>
       </c>
     </row>
     <row r="152">
@@ -3280,16 +3564,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.9998562618801007</v>
+        <v>0.1955591498735787</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0001437381198992629</v>
+        <v>0.4196619512375943</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.384778898888827</v>
       </c>
     </row>
     <row r="153">
@@ -3299,13 +3586,20 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.2468305548581251</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.1633799310374828</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.5897895141043921</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -3314,13 +3608,20 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.1350985191915527</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.0009912694715055574</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.8639102113369417</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -3332,10 +3633,17 @@
         <v>2</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.0921377178566804</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.8345427099512074</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.07331957219211212</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -3344,16 +3652,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1431346806768155</v>
+        <v>0.3845830531241112</v>
       </c>
       <c r="E156" t="n">
-        <v>0.8568653193231845</v>
+        <v>0.04510093262236434</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.5703160142535245</v>
       </c>
     </row>
     <row r="157">
@@ -3363,13 +3674,20 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.3740422108131407</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.1809082871966491</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.4450495019902101</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -3378,16 +3696,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.9998077232223196</v>
+        <v>0.2900583579878934</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0001922767776804378</v>
+        <v>0.007081769460620896</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.7028598725514856</v>
       </c>
     </row>
     <row r="159">
@@ -3397,16 +3718,19 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9999856026041019</v>
+        <v>0.3155074454539471</v>
       </c>
       <c r="E159" t="n">
-        <v>1.439739589810663e-05</v>
+        <v>0.06072007207793152</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.6237724824681213</v>
       </c>
     </row>
     <row r="160">
@@ -3419,10 +3743,17 @@
         <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.2616134561356613</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.3901066357813771</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.3482799080829617</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -3431,13 +3762,20 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.3085482293164097</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.03212281526530655</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.6593289554182837</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -3446,13 +3784,20 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.3579480933940414</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.269398086428251</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.3726538201777077</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -3461,16 +3806,19 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9996568001975953</v>
+        <v>0.4004663775785471</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0003431998024047132</v>
+        <v>0.02867442165339396</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.570859200768059</v>
       </c>
     </row>
     <row r="164">
@@ -3480,13 +3828,20 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.2080309038604524</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.2942073975361352</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.4977616986034123</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -3495,13 +3850,20 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.288308076795568</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.01966808658810791</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.6920238366163241</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -3510,13 +3872,20 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.2127300148433198</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.004305229348030733</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.7829647558086495</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -3525,13 +3894,14 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -3540,13 +3910,20 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.007836192261648021</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.001246170277596521</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.9909176374607556</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -3555,13 +3932,14 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -3570,16 +3948,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9984797193029773</v>
+        <v>0.1992069690429795</v>
       </c>
       <c r="E170" t="n">
-        <v>0.001520280697022683</v>
+        <v>0.01367861936582611</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.7871144115911944</v>
       </c>
     </row>
     <row r="171">
@@ -3589,16 +3970,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.9999326498655766</v>
+        <v>0.1343948307781996</v>
       </c>
       <c r="E171" t="n">
-        <v>6.73501344233865e-05</v>
+        <v>0.0002603104562343655</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.865344858765566</v>
       </c>
     </row>
     <row r="172">
@@ -3608,13 +3992,14 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -3623,13 +4008,20 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.1113368011451938</v>
+      </c>
+      <c r="E173" t="n">
+        <v>7.693321969339523e-05</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.8885862656351127</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -3638,16 +4030,19 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9999897249278328</v>
+        <v>0.3459116240749228</v>
       </c>
       <c r="E174" t="n">
-        <v>1.027507216724078e-05</v>
+        <v>0.0213019220249526</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.6327864539001246</v>
       </c>
     </row>
     <row r="175">
@@ -3657,13 +4052,20 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.2200154114576454</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.0009478325436838686</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.7790367559986706</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -3672,13 +4074,14 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -3687,13 +4090,14 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -3702,13 +4106,14 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -3717,13 +4122,20 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.3485952925510419</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.08663205322256785</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.5647726542263902</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -3732,13 +4144,20 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.3277295790727691</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.3125912632849358</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.3596791576422952</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -3747,16 +4166,19 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.9999994281754256</v>
+        <v>0.2296847961500776</v>
       </c>
       <c r="E181" t="n">
-        <v>5.718245744122648e-07</v>
+        <v>0.5859181785170241</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.1843970253328983</v>
       </c>
     </row>
     <row r="182">
@@ -3766,16 +4188,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.9999705720738402</v>
+        <v>0.1752490127006424</v>
       </c>
       <c r="E182" t="n">
-        <v>2.942792615973333e-05</v>
+        <v>0.0007643629425500086</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.8239866243568077</v>
       </c>
     </row>
     <row r="183">
@@ -3785,16 +4210,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.9999996782440125</v>
+        <v>0.1645127252997299</v>
       </c>
       <c r="E183" t="n">
-        <v>3.217559875038416e-07</v>
+        <v>0.0008610930550278824</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.8346261816452422</v>
       </c>
     </row>
     <row r="184">
@@ -3804,16 +4232,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.9999287201263656</v>
+        <v>0.1118736116027278</v>
       </c>
       <c r="E184" t="n">
-        <v>7.127987363442017e-05</v>
+        <v>0.8404801169049214</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.04764627149235079</v>
       </c>
     </row>
     <row r="185">
@@ -3823,16 +4254,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.9999978732716184</v>
+        <v>0.2247905618680188</v>
       </c>
       <c r="E185" t="n">
-        <v>2.126728381679304e-06</v>
+        <v>0.006070654689879264</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.7691387834421021</v>
       </c>
     </row>
     <row r="186">
@@ -3842,16 +4276,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.9999993973693441</v>
+        <v>0.2028173396144419</v>
       </c>
       <c r="E186" t="n">
-        <v>6.026306559574784e-07</v>
+        <v>0.0002351326597645841</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.7969475277257936</v>
       </c>
     </row>
     <row r="187">
@@ -3861,16 +4298,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.9999988921907721</v>
+        <v>0.3459047660121751</v>
       </c>
       <c r="E187" t="n">
-        <v>1.107809227867349e-06</v>
+        <v>0.04025569682379277</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.6138395371640322</v>
       </c>
     </row>
     <row r="188">
@@ -3880,16 +4320,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.9999938354531119</v>
+        <v>0.3984439621912437</v>
       </c>
       <c r="E188" t="n">
-        <v>6.164546888041099e-06</v>
+        <v>0.1057989824753845</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.4957570553333717</v>
       </c>
     </row>
     <row r="189">
@@ -3899,16 +4342,19 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9999606513544592</v>
+        <v>0.3418434691340411</v>
       </c>
       <c r="E189" t="n">
-        <v>3.934864554080237e-05</v>
+        <v>0.0865960820404645</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.5715604488254944</v>
       </c>
     </row>
     <row r="190">
@@ -3918,16 +4364,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0.9999910060433639</v>
+        <v>0.09687937133286767</v>
       </c>
       <c r="E190" t="n">
-        <v>8.993956636107363e-06</v>
+        <v>0.0004677437151382037</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.9026528849519941</v>
       </c>
     </row>
     <row r="191">
@@ -3937,13 +4386,20 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.2528573500184745</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.00321505575604928</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.7439275942254762</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -3952,13 +4408,14 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -3974,6 +4431,7 @@
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -3989,6 +4447,7 @@
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -4004,6 +4463,7 @@
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -4012,16 +4472,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.9999913778458043</v>
+        <v>0.3257124008316523</v>
       </c>
       <c r="E196" t="n">
-        <v>8.622154195722508e-06</v>
+        <v>0.01923212072979256</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.6550554784385553</v>
       </c>
     </row>
     <row r="197">
@@ -4031,16 +4494,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.9994973988175793</v>
+        <v>0.2462606224302615</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0005026011824207474</v>
+        <v>0.02165497017071011</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.7320844073990285</v>
       </c>
     </row>
     <row r="198">
@@ -4050,13 +4516,20 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.2168342537832422</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.02226979222110437</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.7608959539956534</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -4065,13 +4538,20 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
-      </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.2825452426657915</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.2585012165812954</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.4589535407529131</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -4080,13 +4560,20 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.4102143213540552</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.09867060159769929</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.4911150770482455</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -4095,16 +4582,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.999999990372174</v>
+        <v>0.223475106074007</v>
       </c>
       <c r="E201" t="n">
-        <v>9.627826004250743e-09</v>
+        <v>0.007741486522607499</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.7687834074033855</v>
       </c>
     </row>
     <row r="202">
@@ -4114,16 +4604,19 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.9999998413886719</v>
+        <v>0.2426789400434848</v>
       </c>
       <c r="E202" t="n">
-        <v>1.586113280797064e-07</v>
+        <v>0.01627108576282848</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.7410499741936867</v>
       </c>
     </row>
     <row r="203">
@@ -4133,16 +4626,19 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0.9998751838835129</v>
+        <v>0.3173654219331582</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0001248161164870779</v>
+        <v>0.07273862994533005</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.6098959481215117</v>
       </c>
     </row>
     <row r="204">
@@ -4152,16 +4648,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.9848030179881793</v>
+        <v>0.3679175212362508</v>
       </c>
       <c r="E204" t="n">
-        <v>0.01519698201182074</v>
+        <v>0.1545790539825663</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.4775034247811829</v>
       </c>
     </row>
     <row r="205">
@@ -4177,10 +4676,13 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.0001061551887969747</v>
+        <v>0.2610280721694918</v>
       </c>
       <c r="E205" t="n">
-        <v>0.999893844811203</v>
+        <v>0.5599750416695336</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.1789968861609746</v>
       </c>
     </row>
     <row r="206">
@@ -4190,13 +4692,14 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -4205,16 +4708,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.9999967096747961</v>
+        <v>0.4020110226781481</v>
       </c>
       <c r="E207" t="n">
-        <v>3.290325203828566e-06</v>
+        <v>0.005848113574715968</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.5921408637471359</v>
       </c>
     </row>
     <row r="208">
@@ -4224,16 +4730,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.999999949483775</v>
+        <v>0.2358334599786893</v>
       </c>
       <c r="E208" t="n">
-        <v>5.05162250307012e-08</v>
+        <v>0.004653321935142892</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.7595132180861678</v>
       </c>
     </row>
     <row r="209">
@@ -4243,13 +4752,20 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.2696698731565867</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.003144868879835943</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.7271852579635772</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -4258,13 +4774,20 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.3689263369127135</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.0007856685772858343</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.6302879945100005</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -4273,13 +4796,14 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -4295,6 +4819,7 @@
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -4303,13 +4828,20 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.3084186695986151</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.0288427803706757</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.6627385500307093</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -4318,16 +4850,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.9999989309557905</v>
+        <v>0.1816658060981039</v>
       </c>
       <c r="E214" t="n">
-        <v>1.069044209457146e-06</v>
+        <v>0.01859525583990968</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.7997389380619865</v>
       </c>
     </row>
     <row r="215">
@@ -4337,13 +4872,20 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.2339785037042974</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.03822167308069239</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.7277998232150102</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -4352,13 +4894,20 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.2243796653918598</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.005064630452769158</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.7705557041553711</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -4367,16 +4916,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.9997659836462298</v>
+        <v>0.2004096487563415</v>
       </c>
       <c r="E217" t="n">
-        <v>0.000234016353770136</v>
+        <v>0.1712548315786562</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.6283355196650023</v>
       </c>
     </row>
     <row r="218">
@@ -4386,13 +4938,14 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -4401,13 +4954,20 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.1741945493329403</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.01390027383431994</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.8119051768327397</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -4422,10 +4982,13 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>9.273605414694686e-07</v>
+        <v>0.0005505365568703289</v>
       </c>
       <c r="E220" t="n">
-        <v>0.9999990726394585</v>
+        <v>0.9992614488612334</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.0001880145818963085</v>
       </c>
     </row>
     <row r="221">
@@ -4435,16 +4998,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.00330688959420089</v>
+        <v>0.1219091035724472</v>
       </c>
       <c r="E221" t="n">
-        <v>0.9966931104057991</v>
+        <v>0.006489319987483856</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.8716015764400691</v>
       </c>
     </row>
     <row r="222">
@@ -4454,16 +5020,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.9963520780223607</v>
+        <v>0.197072826870744</v>
       </c>
       <c r="E222" t="n">
-        <v>0.003647921977639254</v>
+        <v>0.05118324439645949</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.7517439287327966</v>
       </c>
     </row>
     <row r="223">
@@ -4479,10 +5048,13 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>8.721787847498774e-07</v>
+        <v>0.001603603584286207</v>
       </c>
       <c r="E223" t="n">
-        <v>0.9999991278212153</v>
+        <v>0.9974884377444313</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.0009079586712824536</v>
       </c>
     </row>
     <row r="224">
@@ -4492,16 +5064,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.9968637812174057</v>
+        <v>0.2174086206338617</v>
       </c>
       <c r="E224" t="n">
-        <v>0.003136218782594262</v>
+        <v>0.2942876533720278</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.4883037259941107</v>
       </c>
     </row>
     <row r="225">
@@ -4511,16 +5086,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.9999995496270824</v>
+        <v>0.3305774438420523</v>
       </c>
       <c r="E225" t="n">
-        <v>4.503729176043738e-07</v>
+        <v>0.09715896828895797</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.5722635878689898</v>
       </c>
     </row>
     <row r="226">
@@ -4536,10 +5114,13 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>5.800615581030844e-05</v>
+        <v>0.008596493819600483</v>
       </c>
       <c r="E226" t="n">
-        <v>0.9999419938441897</v>
+        <v>0.9859584501024643</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.00544505607793527</v>
       </c>
     </row>
     <row r="227">
@@ -4549,16 +5130,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2753272855625718</v>
+        <v>0.1862512547780277</v>
       </c>
       <c r="E227" t="n">
-        <v>0.7246727144374282</v>
+        <v>0.01133732068160032</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.802411424540372</v>
       </c>
     </row>
     <row r="228">
@@ -4568,16 +5152,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.8095068542021033</v>
+        <v>0.134919520254394</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1904931457978966</v>
+        <v>0.00211561056899745</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.8629648691766084</v>
       </c>
     </row>
     <row r="229">
@@ -4593,10 +5180,13 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>2.705686190307421e-05</v>
+        <v>0.01719223613501505</v>
       </c>
       <c r="E229" t="n">
-        <v>0.9999729431380969</v>
+        <v>0.9186725746741334</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.06413518919085151</v>
       </c>
     </row>
     <row r="230">
@@ -4606,16 +5196,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.9999998759677828</v>
+        <v>0.251038095066254</v>
       </c>
       <c r="E230" t="n">
-        <v>1.240322171586393e-07</v>
+        <v>0.001715152630703736</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.7472467523030422</v>
       </c>
     </row>
     <row r="231">
@@ -4625,16 +5218,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.9999995375382074</v>
+        <v>0.143171216149737</v>
       </c>
       <c r="E231" t="n">
-        <v>4.624617926037675e-07</v>
+        <v>0.002604967562944585</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.8542238162873185</v>
       </c>
     </row>
     <row r="232">
@@ -4644,16 +5240,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.9208684146835484</v>
+        <v>0.08668723084987294</v>
       </c>
       <c r="E232" t="n">
-        <v>0.07913158531645162</v>
+        <v>0.0001603063661916543</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.9131524627839355</v>
       </c>
     </row>
     <row r="233">
@@ -4663,16 +5262,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.01299040667417606</v>
+        <v>0.4649960359916412</v>
       </c>
       <c r="E233" t="n">
-        <v>0.9870095933258239</v>
+        <v>0.1104844156505005</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.4245195483578583</v>
       </c>
     </row>
     <row r="234">
@@ -4682,16 +5284,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0.9999973670916658</v>
+        <v>0.2137964484286997</v>
       </c>
       <c r="E234" t="n">
-        <v>2.632908334202288e-06</v>
+        <v>9.231282980423485e-05</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.786111238741496</v>
       </c>
     </row>
     <row r="235">
@@ -4701,16 +5306,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0.9999743748481901</v>
+        <v>0.1593292369032337</v>
       </c>
       <c r="E235" t="n">
-        <v>2.562515180990684e-05</v>
+        <v>7.843464619671383e-05</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.8405923284505696</v>
       </c>
     </row>
     <row r="236">
@@ -4720,16 +5328,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.9992404541055629</v>
+        <v>0.2557230409357482</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0007595458944370133</v>
+        <v>0.008784686908301023</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.7354922721559508</v>
       </c>
     </row>
     <row r="237">
@@ -4739,22 +5350,25 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.999998733897256</v>
+        <v>0.08645961758630934</v>
       </c>
       <c r="E237" t="n">
-        <v>1.266102744004618e-06</v>
+        <v>2.84862536424386e-05</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.9135118961600484</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
